--- a/outputs/validation_truss_fab_error.xlsx
+++ b/outputs/validation_truss_fab_error.xlsx
@@ -538,7 +538,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.676274217120448e-17</v>
+        <v>-4.340689376152277e-19</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -556,7 +556,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1.676274217120448e-17</v>
+        <v>4.340689376152277e-19</v>
       </c>
     </row>
     <row r="4">
@@ -573,13 +573,13 @@
         <v>2.598076211353316</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.93310952988333e-16</v>
+        <v>-1.609820512624577e-17</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002499999999999709</v>
+        <v>0.002500000000000045</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.004330127018921833</v>
+        <v>-0.004330127018922291</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -591,7 +591,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004999999999999542</v>
+        <v>0.005000000000000108</v>
       </c>
     </row>
     <row r="5">
@@ -608,13 +608,13 @@
         <v>2.598076211353316</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.925891125394515e-16</v>
+        <v>-1.58091034875743e-17</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.002499999999999708</v>
+        <v>-0.002500000000000048</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004330127018921839</v>
+        <v>0.004330127018922295</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -626,7 +626,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.004999999999999546</v>
+        <v>0.005000000000000112</v>
       </c>
     </row>
     <row r="6">
@@ -643,13 +643,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-6.656716817340045e-16</v>
+        <v>4.217979690080612e-17</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.662702988502231e-16</v>
+        <v>2.496555289566721e-17</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.005773502691895882</v>
+        <v>-0.005773502691896366</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005773502691895882</v>
+        <v>0.005773502691896366</v>
       </c>
     </row>
     <row r="7">
@@ -678,13 +678,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-6.6479308875418e-16</v>
+        <v>4.237319201299675e-17</v>
       </c>
       <c r="F7" t="n">
-        <v>2.654651198196905e-16</v>
+        <v>-2.715856455137496e-17</v>
       </c>
       <c r="G7" t="n">
-        <v>0.005773502691895886</v>
+        <v>0.00577350269189637</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -696,7 +696,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.005773502691895886</v>
+        <v>0.00577350269189637</v>
       </c>
     </row>
     <row r="8">
@@ -713,13 +713,13 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E8" t="n">
-        <v>-5.60108479708646e-16</v>
+        <v>-6.640573517909717e-17</v>
       </c>
       <c r="F8" t="n">
-        <v>0.004999999999999626</v>
+        <v>0.005000000000000042</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.008660254037843948</v>
+        <v>-0.008660254037844501</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -731,7 +731,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.009999999999999433</v>
+        <v>0.01000000000000012</v>
       </c>
     </row>
     <row r="9">
@@ -748,13 +748,13 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.600381307339044e-16</v>
+        <v>-6.63157692652396e-17</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.004999999999999622</v>
+        <v>-0.005000000000000043</v>
       </c>
       <c r="G9" t="n">
-        <v>0.008660254037843944</v>
+        <v>0.008660254037844498</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -766,7 +766,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009999999999999428</v>
+        <v>0.01000000000000012</v>
       </c>
     </row>
     <row r="10">
@@ -783,13 +783,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01999999999999778</v>
+        <v>0.02000000000000019</v>
       </c>
       <c r="F10" t="n">
-        <v>0.009999999999999551</v>
+        <v>0.01000000000000005</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.005773502691895869</v>
+        <v>-0.005773502691896375</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -801,7 +801,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.02309401076758282</v>
+        <v>0.02309401076758525</v>
       </c>
     </row>
     <row r="11">
@@ -818,13 +818,13 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01999999999999778</v>
+        <v>0.02000000000000019</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.009999999999999554</v>
+        <v>-0.01000000000000005</v>
       </c>
       <c r="G11" t="n">
-        <v>0.005773502691895859</v>
+        <v>0.005773502691896366</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -836,7 +836,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.02309401076758282</v>
+        <v>0.02309401076758524</v>
       </c>
     </row>
     <row r="12">
@@ -853,13 +853,13 @@
         <v>2.598076211353316</v>
       </c>
       <c r="E12" t="n">
-        <v>0.02999999999999752</v>
+        <v>0.03000000000000024</v>
       </c>
       <c r="F12" t="n">
-        <v>0.007499999999999598</v>
+        <v>0.007500000000000032</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.004330127018921832</v>
+        <v>-0.004330127018922303</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -871,7 +871,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.03122498999198946</v>
+        <v>0.03122498999199224</v>
       </c>
     </row>
     <row r="13">
@@ -888,13 +888,13 @@
         <v>2.598076211353316</v>
       </c>
       <c r="E13" t="n">
-        <v>0.02999999999999752</v>
+        <v>0.03000000000000023</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.007499999999999597</v>
+        <v>-0.007500000000000036</v>
       </c>
       <c r="G13" t="n">
-        <v>0.004330127018921823</v>
+        <v>0.004330127018922292</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -906,7 +906,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.03122498999198946</v>
+        <v>0.03122498999199224</v>
       </c>
     </row>
     <row r="14">
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.05999999999999572</v>
+        <v>0.0600000000000005</v>
       </c>
       <c r="F14" t="n">
-        <v>0.009999999999999454</v>
+        <v>0.01000000000000008</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -941,7 +941,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.06082762530297788</v>
+        <v>0.0608276253029827</v>
       </c>
     </row>
     <row r="15">
@@ -958,10 +958,10 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.05999999999999572</v>
+        <v>0.0600000000000005</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.009999999999999452</v>
+        <v>-0.01000000000000008</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -976,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.06082762530297788</v>
+        <v>0.0608276253029827</v>
       </c>
     </row>
   </sheetData>
@@ -1032,16 +1032,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>0.06082762530297788</v>
+        <v>0.0608276253029827</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05999999999999572</v>
+        <v>0.0600000000000005</v>
       </c>
       <c r="E2" t="n">
-        <v>0.009999999999999454</v>
+        <v>-0.01000000000000008</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -1054,16 +1054,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>0.05999999999999572</v>
+        <v>0.0600000000000005</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05999999999999572</v>
+        <v>0.0600000000000005</v>
       </c>
       <c r="E3" t="n">
-        <v>0.009999999999999454</v>
+        <v>-0.01000000000000008</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.009999999999999554</v>
+        <v>-0.01000000000000008</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01999999999999778</v>
+        <v>0.0600000000000005</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.009999999999999554</v>
+        <v>-0.01000000000000008</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005773502691895859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1101,16 +1101,16 @@
         <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.008660254037843948</v>
+        <v>-0.008660254037844501</v>
       </c>
       <c r="D5" t="n">
-        <v>-5.60108479708646e-16</v>
+        <v>-6.640573517909717e-17</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004999999999999626</v>
+        <v>0.005000000000000042</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.008660254037843948</v>
+        <v>-0.008660254037844501</v>
       </c>
     </row>
   </sheetData>
@@ -1154,13 +1154,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>3.389288849575678e-12</v>
+        <v>1.4210854715202e-13</v>
       </c>
       <c r="C2" t="n">
-        <v>1.91278104466619e-11</v>
+        <v>-5.115907697472721e-13</v>
       </c>
       <c r="D2" t="n">
-        <v>2.586375558166765e-12</v>
+        <v>2.629008122312371e-13</v>
       </c>
     </row>
     <row r="3">
@@ -1169,10 +1169,10 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>-1.875832822406664e-11</v>
+        <v>7.389644451905042e-13</v>
       </c>
       <c r="D3" t="n">
-        <v>-2.557953848736361e-12</v>
+        <v>-2.273736754432321e-13</v>
       </c>
     </row>
     <row r="4">
@@ -1182,7 +1182,7 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>-2.046363078989089e-12</v>
+        <v>3.410605131648481e-13</v>
       </c>
     </row>
     <row r="5">
@@ -1192,7 +1192,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>2.273736754432321e-12</v>
+        <v>-2.273736754432321e-13</v>
       </c>
     </row>
   </sheetData>
@@ -1275,16 +1275,16 @@
         <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.662702988502231e-16</v>
+        <v>2.496555289566721e-17</v>
       </c>
       <c r="G2" t="n">
-        <v>-4.437838314170385e-17</v>
+        <v>4.160925482611201e-18</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.242594727967708e-11</v>
+        <v>1.165059135131136e-12</v>
       </c>
       <c r="I2" t="n">
-        <v>-3.10648681991927e-09</v>
+        <v>2.912647837827841e-10</v>
       </c>
     </row>
     <row r="3">
@@ -1306,16 +1306,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F3" t="n">
-        <v>-7.24247051220317e-17</v>
+        <v>-9.974659986866641e-18</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.393814099939475e-17</v>
+        <v>-1.919624209497481e-18</v>
       </c>
       <c r="H3" t="n">
-        <v>-3.902679479830532e-12</v>
+        <v>-5.374947786592948e-13</v>
       </c>
       <c r="I3" t="n">
-        <v>-9.756698699576329e-10</v>
+        <v>-1.343736946648237e-10</v>
       </c>
     </row>
     <row r="4">
@@ -1337,16 +1337,16 @@
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>-1.734723475976807e-18</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>-5.782411586589357e-19</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>-1.61907524424502e-13</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>-4.04768811061255e-11</v>
       </c>
     </row>
     <row r="5">
@@ -1368,16 +1368,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.165870343657673e-17</v>
+        <v>-1.170938346284345e-17</v>
       </c>
       <c r="G5" t="n">
-        <v>-6.092720317100702e-18</v>
+        <v>-2.253471898105739e-18</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.705961688788196e-12</v>
+        <v>-6.309721314696069e-13</v>
       </c>
       <c r="I5" t="n">
-        <v>-4.264904221970491e-10</v>
+        <v>-1.577430328674017e-10</v>
       </c>
     </row>
     <row r="6">
@@ -1399,16 +1399,16 @@
         <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>8.673617379884035e-19</v>
+        <v>2.602085213965211e-18</v>
       </c>
       <c r="G6" t="n">
-        <v>1.445602896647339e-19</v>
+        <v>4.336808689942018e-19</v>
       </c>
       <c r="H6" t="n">
-        <v>4.04768811061255e-14</v>
+        <v>1.214306433183765e-13</v>
       </c>
       <c r="I6" t="n">
-        <v>1.011922027653137e-11</v>
+        <v>3.035766082959412e-11</v>
       </c>
     </row>
     <row r="7">
@@ -1430,16 +1430,16 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>0.009999999999999816</v>
+        <v>0.01000000000000003</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001666666666666636</v>
+        <v>0.001666666666666671</v>
       </c>
       <c r="H7" t="n">
-        <v>466.666666666658</v>
+        <v>466.6666666666679</v>
       </c>
       <c r="I7" t="n">
-        <v>116666.6666666645</v>
+        <v>116666.666666667</v>
       </c>
     </row>
     <row r="8">
@@ -1461,16 +1461,16 @@
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>8.673617379884035e-18</v>
       </c>
       <c r="G8" t="n">
-        <v>1.156482317317871e-18</v>
+        <v>1.445602896647339e-18</v>
       </c>
       <c r="H8" t="n">
-        <v>3.23815048849004e-13</v>
+        <v>4.04768811061255e-13</v>
       </c>
       <c r="I8" t="n">
-        <v>8.095376221225099e-11</v>
+        <v>1.011922027653137e-10</v>
       </c>
     </row>
     <row r="9">
@@ -1492,16 +1492,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F9" t="n">
-        <v>1.387778780781446e-17</v>
+        <v>-1.214306433183765e-17</v>
       </c>
       <c r="G9" t="n">
-        <v>2.670781508866061e-18</v>
+        <v>-2.336933820257803e-18</v>
       </c>
       <c r="H9" t="n">
-        <v>7.478188224824971e-13</v>
+        <v>-6.54341469672185e-13</v>
       </c>
       <c r="I9" t="n">
-        <v>1.869547056206243e-10</v>
+        <v>-1.635853674180462e-10</v>
       </c>
     </row>
     <row r="10">
@@ -1523,16 +1523,16 @@
         <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>4.336808689942018e-19</v>
+        <v>-2.602085213965211e-18</v>
       </c>
       <c r="G10" t="n">
-        <v>1.445602896647339e-19</v>
+        <v>-8.673617379884035e-19</v>
       </c>
       <c r="H10" t="n">
-        <v>4.04768811061255e-14</v>
+        <v>-2.42861286636753e-13</v>
       </c>
       <c r="I10" t="n">
-        <v>1.011922027653137e-11</v>
+        <v>-6.071532165918825e-11</v>
       </c>
     </row>
     <row r="11">
@@ -1554,16 +1554,16 @@
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>-9.71445146547012e-17</v>
+        <v>2.775557561562891e-17</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.61907524424502e-17</v>
+        <v>4.625929269271485e-18</v>
       </c>
       <c r="H11" t="n">
-        <v>-4.533410683886055e-12</v>
+        <v>1.295260195396016e-12</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.133352670971514e-09</v>
+        <v>3.23815048849004e-10</v>
       </c>
     </row>
     <row r="12">
@@ -1585,16 +1585,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F12" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>-1.214306433183765e-17</v>
       </c>
       <c r="G12" t="n">
-        <v>1.068312603546424e-17</v>
+        <v>-2.336933820257803e-18</v>
       </c>
       <c r="H12" t="n">
-        <v>2.991275289929988e-12</v>
+        <v>-6.54341469672185e-13</v>
       </c>
       <c r="I12" t="n">
-        <v>7.47818822482497e-10</v>
+        <v>-1.635853674180462e-10</v>
       </c>
     </row>
     <row r="13">
@@ -1616,16 +1616,16 @@
         <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>2.654651198196905e-16</v>
+        <v>-2.715856455137496e-17</v>
       </c>
       <c r="G13" t="n">
-        <v>4.424418663661508e-17</v>
+        <v>-4.526427425229161e-18</v>
       </c>
       <c r="H13" t="n">
-        <v>1.238837225825222e-11</v>
+        <v>-1.267399679064165e-12</v>
       </c>
       <c r="I13" t="n">
-        <v>3.097093064563055e-09</v>
+        <v>-3.168499197660412e-10</v>
       </c>
     </row>
     <row r="14">
@@ -1647,16 +1647,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F14" t="n">
-        <v>7.589415207398531e-17</v>
+        <v>9.107298248878237e-18</v>
       </c>
       <c r="G14" t="n">
-        <v>1.460583637661127e-17</v>
+        <v>1.752700365193353e-18</v>
       </c>
       <c r="H14" t="n">
-        <v>4.089634185451156e-12</v>
+        <v>4.907561022541388e-13</v>
       </c>
       <c r="I14" t="n">
-        <v>1.022408546362789e-09</v>
+        <v>1.226890255635347e-10</v>
       </c>
     </row>
     <row r="15">
@@ -1678,16 +1678,16 @@
         <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>1.734723475976807e-18</v>
+        <v>8.673617379884035e-19</v>
       </c>
       <c r="G15" t="n">
-        <v>5.782411586589357e-19</v>
+        <v>2.891205793294678e-19</v>
       </c>
       <c r="H15" t="n">
-        <v>1.61907524424502e-13</v>
+        <v>8.095376221225099e-14</v>
       </c>
       <c r="I15" t="n">
-        <v>4.04768811061255e-11</v>
+        <v>2.023844055306275e-11</v>
       </c>
     </row>
     <row r="16">
@@ -1709,16 +1709,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F16" t="n">
-        <v>3.079134169858833e-17</v>
+        <v>9.974659986866641e-18</v>
       </c>
       <c r="G16" t="n">
-        <v>5.925796472796573e-18</v>
+        <v>1.919624209497481e-18</v>
       </c>
       <c r="H16" t="n">
-        <v>1.65922301238304e-12</v>
+        <v>5.374947786592948e-13</v>
       </c>
       <c r="I16" t="n">
-        <v>4.148057530957601e-10</v>
+        <v>1.343736946648237e-10</v>
       </c>
     </row>
     <row r="17">
@@ -1740,16 +1740,16 @@
         <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>-4.336808689942018e-18</v>
+        <v>-7.806255641895632e-18</v>
       </c>
       <c r="G17" t="n">
-        <v>-7.228014483236697e-19</v>
+        <v>-1.301042606982605e-18</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.023844055306275e-13</v>
+        <v>-3.642919299551295e-13</v>
       </c>
       <c r="I17" t="n">
-        <v>-5.059610138265687e-11</v>
+        <v>-9.107298248878237e-11</v>
       </c>
     </row>
     <row r="18">
@@ -1771,16 +1771,16 @@
         <v>6</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.00999999999999982</v>
+        <v>-0.01000000000000003</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.001666666666666637</v>
+        <v>-0.001666666666666671</v>
       </c>
       <c r="H18" t="n">
-        <v>-466.6666666666582</v>
+        <v>-466.6666666666679</v>
       </c>
       <c r="I18" t="n">
-        <v>-116666.6666666645</v>
+        <v>-116666.666666667</v>
       </c>
     </row>
     <row r="19">
@@ -1802,16 +1802,16 @@
         <v>6</v>
       </c>
       <c r="F19" t="n">
-        <v>-5.204170427930421e-18</v>
+        <v>-1.734723475976807e-18</v>
       </c>
       <c r="G19" t="n">
-        <v>-8.673617379884035e-19</v>
+        <v>-2.891205793294678e-19</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.42861286636753e-13</v>
+        <v>-8.095376221225099e-14</v>
       </c>
       <c r="I19" t="n">
-        <v>-6.071532165918825e-11</v>
+        <v>-2.023844055306275e-11</v>
       </c>
     </row>
     <row r="20">
@@ -1833,16 +1833,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.387778780781446e-17</v>
+        <v>1.214306433183765e-17</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.670781508866061e-18</v>
+        <v>2.336933820257803e-18</v>
       </c>
       <c r="H20" t="n">
-        <v>-7.478188224824971e-13</v>
+        <v>6.54341469672185e-13</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.869547056206243e-10</v>
+        <v>1.635853674180462e-10</v>
       </c>
     </row>
     <row r="21">
@@ -1864,16 +1864,16 @@
         <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>3.035766082959412e-18</v>
+        <v>8.673617379884035e-19</v>
       </c>
       <c r="G21" t="n">
-        <v>1.011922027653138e-18</v>
+        <v>2.891205793294678e-19</v>
       </c>
       <c r="H21" t="n">
-        <v>2.833381677428785e-13</v>
+        <v>8.095376221225099e-14</v>
       </c>
       <c r="I21" t="n">
-        <v>7.083454193571961e-11</v>
+        <v>2.023844055306275e-11</v>
       </c>
     </row>
     <row r="22">
@@ -1895,16 +1895,16 @@
         <v>6</v>
       </c>
       <c r="F22" t="n">
-        <v>1.023486850826316e-16</v>
+        <v>-2.949029909160572e-17</v>
       </c>
       <c r="G22" t="n">
-        <v>1.70581141804386e-17</v>
+        <v>-4.915049848600954e-18</v>
       </c>
       <c r="H22" t="n">
-        <v>4.776271970522808e-12</v>
+        <v>-1.376213957608267e-12</v>
       </c>
       <c r="I22" t="n">
-        <v>1.194067992630702e-09</v>
+        <v>-3.440534894020667e-10</v>
       </c>
     </row>
     <row r="23">
@@ -1926,16 +1926,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.898059818321144e-17</v>
+        <v>8.673617379884035e-18</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.135082141268076e-17</v>
+        <v>1.669238443041288e-18</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.178229995550613e-12</v>
+        <v>4.673867640515606e-13</v>
       </c>
       <c r="I23" t="n">
-        <v>-7.945574988876531e-10</v>
+        <v>1.168466910128902e-10</v>
       </c>
     </row>
     <row r="24">
@@ -1957,16 +1957,16 @@
         <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.676274217120448e-17</v>
+        <v>-4.340689376152277e-19</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.587580723734825e-18</v>
+        <v>-1.446896458717426e-19</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.564522602645751e-12</v>
+        <v>-4.051310084408792e-14</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.911306506614377e-10</v>
+        <v>-1.012827521102198e-11</v>
       </c>
     </row>
     <row r="25">
@@ -1988,16 +1988,16 @@
         <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>7.218404488814572e-19</v>
+        <v>2.891016386714714e-19</v>
       </c>
       <c r="G25" t="n">
-        <v>2.406134829604857e-19</v>
+        <v>9.636721289049048e-20</v>
       </c>
       <c r="H25" t="n">
-        <v>6.7371775228936e-14</v>
+        <v>2.698281960933733e-14</v>
       </c>
       <c r="I25" t="n">
-        <v>1.6842943807234e-11</v>
+        <v>6.745704902334333e-12</v>
       </c>
     </row>
     <row r="26">
@@ -2019,16 +2019,16 @@
         <v>3</v>
       </c>
       <c r="F26" t="n">
-        <v>8.785929798245307e-19</v>
+        <v>1.933951121906287e-19</v>
       </c>
       <c r="G26" t="n">
-        <v>2.928643266081769e-19</v>
+        <v>6.446503739687624e-20</v>
       </c>
       <c r="H26" t="n">
-        <v>8.200201145028953e-14</v>
+        <v>1.805021047112535e-14</v>
       </c>
       <c r="I26" t="n">
-        <v>2.050050286257238e-11</v>
+        <v>4.512552617781336e-12</v>
       </c>
     </row>
     <row r="27">
@@ -2050,16 +2050,16 @@
         <v>3</v>
       </c>
       <c r="F27" t="n">
-        <v>7.034897474159622e-20</v>
+        <v>8.996591385756622e-20</v>
       </c>
       <c r="G27" t="n">
-        <v>2.344965824719874e-20</v>
+        <v>2.998863795252207e-20</v>
       </c>
       <c r="H27" t="n">
-        <v>6.565904309215647e-15</v>
+        <v>8.39681862670618e-15</v>
       </c>
       <c r="I27" t="n">
-        <v>1.641476077303912e-12</v>
+        <v>2.099204656676545e-12</v>
       </c>
     </row>
     <row r="28">
@@ -2143,16 +2143,16 @@
         <v>3</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>6.938893903907228e-18</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>2.312964634635743e-18</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>6.476300976980079e-13</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1.61907524424502e-10</v>
       </c>
     </row>
     <row r="31">
@@ -2174,16 +2174,16 @@
         <v>6</v>
       </c>
       <c r="F31" t="n">
-        <v>-3.057450126409123e-17</v>
+        <v>2.168404344971009e-19</v>
       </c>
       <c r="G31" t="n">
-        <v>-5.095750210681871e-18</v>
+        <v>3.614007241618348e-20</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.426810058990924e-12</v>
+        <v>1.011922027653137e-14</v>
       </c>
       <c r="I31" t="n">
-        <v>-3.56702514747731e-10</v>
+        <v>2.529805069132844e-12</v>
       </c>
     </row>
     <row r="32">
@@ -2205,16 +2205,16 @@
         <v>6</v>
       </c>
       <c r="F32" t="n">
-        <v>2.54457366959455e-17</v>
+        <v>-1.084396206796017e-18</v>
       </c>
       <c r="G32" t="n">
-        <v>4.240956115990917e-18</v>
+        <v>-1.807327011326696e-19</v>
       </c>
       <c r="H32" t="n">
-        <v>1.187467712477457e-12</v>
+        <v>-5.060515631714747e-14</v>
       </c>
       <c r="I32" t="n">
-        <v>2.968669281193641e-10</v>
+        <v>-1.265128907928687e-11</v>
       </c>
     </row>
     <row r="33">
@@ -2236,16 +2236,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F33" t="n">
-        <v>-5.986528605649763e-17</v>
+        <v>-5.341491050333823e-18</v>
       </c>
       <c r="G33" t="n">
-        <v>-8.924189940986602e-18</v>
+        <v>-7.962624726502119e-19</v>
       </c>
       <c r="H33" t="n">
-        <v>-2.498773183476249e-12</v>
+        <v>-2.229534923420594e-13</v>
       </c>
       <c r="I33" t="n">
-        <v>-6.246932958690621e-10</v>
+        <v>-5.573837308551484e-11</v>
       </c>
     </row>
     <row r="34">
@@ -2267,16 +2267,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F34" t="n">
-        <v>5.204150456663151e-17</v>
+        <v>3.272369188478197e-18</v>
       </c>
       <c r="G34" t="n">
-        <v>7.757889457490252e-18</v>
+        <v>4.878159968608712e-19</v>
       </c>
       <c r="H34" t="n">
-        <v>2.172209048097271e-12</v>
+        <v>1.36588479121044e-13</v>
       </c>
       <c r="I34" t="n">
-        <v>5.430522620243177e-10</v>
+        <v>3.414711978026099e-11</v>
       </c>
     </row>
     <row r="35">
@@ -2298,16 +2298,16 @@
         <v>6</v>
       </c>
       <c r="F35" t="n">
-        <v>-2.818925648462312e-17</v>
+        <v>4.336808689942018e-19</v>
       </c>
       <c r="G35" t="n">
-        <v>-4.698209414103853e-18</v>
+        <v>7.228014483236696e-20</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.315498635949079e-12</v>
+        <v>2.023844055306275e-14</v>
       </c>
       <c r="I35" t="n">
-        <v>-3.288746589872696e-10</v>
+        <v>5.059610138265687e-12</v>
       </c>
     </row>
     <row r="36">
@@ -2329,16 +2329,16 @@
         <v>6</v>
       </c>
       <c r="F36" t="n">
-        <v>2.753873518113181e-17</v>
+        <v>-1.084202172485504e-18</v>
       </c>
       <c r="G36" t="n">
-        <v>4.589789196855302e-18</v>
+        <v>-1.807003620809174e-19</v>
       </c>
       <c r="H36" t="n">
-        <v>1.285140975119484e-12</v>
+        <v>-5.059610138265687e-14</v>
       </c>
       <c r="I36" t="n">
-        <v>3.212852437798711e-10</v>
+        <v>-1.264902534566422e-11</v>
       </c>
     </row>
     <row r="37">
@@ -2360,16 +2360,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F37" t="n">
-        <v>-5.741860712598695e-17</v>
+        <v>-3.029331506209172e-18</v>
       </c>
       <c r="G37" t="n">
-        <v>-8.55946058047071e-18</v>
+        <v>-4.51586078284369e-19</v>
       </c>
       <c r="H37" t="n">
-        <v>-2.396648962531799e-12</v>
+        <v>-1.264441019196233e-13</v>
       </c>
       <c r="I37" t="n">
-        <v>-5.991622406329497e-10</v>
+        <v>-3.161102547990584e-11</v>
       </c>
     </row>
     <row r="38">
@@ -2391,16 +2391,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F38" t="n">
-        <v>5.506225291805303e-17</v>
+        <v>3.342586208752015e-18</v>
       </c>
       <c r="G38" t="n">
-        <v>8.208196034603516e-18</v>
+        <v>4.982833322281873e-19</v>
       </c>
       <c r="H38" t="n">
-        <v>2.298294889688984e-12</v>
+        <v>1.395193330238924e-13</v>
       </c>
       <c r="I38" t="n">
-        <v>5.745737224222461e-10</v>
+        <v>3.48798332559731e-11</v>
       </c>
     </row>
     <row r="39">
@@ -2422,16 +2422,16 @@
         <v>6</v>
       </c>
       <c r="F39" t="n">
-        <v>-2.949029909160572e-17</v>
+        <v>-8.673617379884035e-19</v>
       </c>
       <c r="G39" t="n">
-        <v>-4.915049848600954e-18</v>
+        <v>-1.445602896647339e-19</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.376213957608267e-12</v>
+        <v>-4.04768811061255e-14</v>
       </c>
       <c r="I39" t="n">
-        <v>-3.440534894020667e-10</v>
+        <v>-1.011922027653137e-11</v>
       </c>
     </row>
     <row r="40">
@@ -2453,16 +2453,16 @@
         <v>6</v>
       </c>
       <c r="F40" t="n">
-        <v>2.688821387764051e-17</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>4.481368979606752e-18</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1.25478331428989e-12</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>3.136958285724726e-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2484,16 +2484,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F41" t="n">
-        <v>-3.469446951953614e-17</v>
+        <v>1.734723475976807e-17</v>
       </c>
       <c r="G41" t="n">
-        <v>-5.171946152598485e-18</v>
+        <v>2.585973076299243e-18</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.448144922727576e-12</v>
+        <v>7.24072461363788e-13</v>
       </c>
       <c r="I41" t="n">
-        <v>-3.62036230681894e-10</v>
+        <v>1.81018115340947e-10</v>
       </c>
     </row>
     <row r="42">
@@ -2515,16 +2515,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F42" t="n">
-        <v>3.816391647148976e-17</v>
+        <v>-1.387778780781446e-17</v>
       </c>
       <c r="G42" t="n">
-        <v>5.689140767858334e-18</v>
+        <v>-2.068778461039394e-18</v>
       </c>
       <c r="H42" t="n">
-        <v>1.592959415000334e-12</v>
+        <v>-5.792579690910304e-13</v>
       </c>
       <c r="I42" t="n">
-        <v>3.982398537500833e-10</v>
+        <v>-1.448144922727576e-10</v>
       </c>
     </row>
     <row r="43">
@@ -2546,16 +2546,16 @@
         <v>6</v>
       </c>
       <c r="F43" t="n">
-        <v>-3.469446951953614e-17</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>-5.782411586589357e-18</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>-1.61907524424502e-12</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>-4.04768811061255e-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2577,16 +2577,16 @@
         <v>6</v>
       </c>
       <c r="F44" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>4.625929269271485e-18</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>1.295260195396016e-12</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>3.23815048849004e-10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2829,10 +2829,10 @@
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.242594727967708e-11</v>
+        <v>1.165059135131136e-12</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.10648681991927e-09</v>
+        <v>2.912647837827841e-10</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -2853,13 +2853,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-6.656716817340045e-16</v>
+        <v>4.217979690080612e-17</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.662702988502231e-16</v>
+        <v>2.496555289566721e-17</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.005773502691895882</v>
+        <v>-0.005773502691896366</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -2889,13 +2889,13 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-2.662702988502231e-16</v>
+        <v>2.496555289566721e-17</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.656716817340045e-16</v>
+        <v>-4.217979690080612e-17</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.005773502691895882</v>
+        <v>-0.005773502691896366</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -2907,7 +2907,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.242594727967708e-11</v>
+        <v>-1.165059135131137e-12</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -2925,7 +2925,7 @@
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>-1.242594727967708e-11</v>
+        <v>1.165059135131137e-12</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -2957,10 +2957,10 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.902679479830532e-12</v>
+        <v>-5.374947786592948e-13</v>
       </c>
       <c r="F3" t="n">
-        <v>-9.756698699576329e-10</v>
+        <v>-1.343736946648237e-10</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -2981,13 +2981,13 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.93310952988333e-16</v>
+        <v>-1.609820512624577e-17</v>
       </c>
       <c r="N3" t="n">
-        <v>0.002499999999999709</v>
+        <v>0.002500000000000045</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.004330127018921833</v>
+        <v>-0.004330127018922291</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -3017,13 +3017,13 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-7.24247051220317e-17</v>
+        <v>-9.974659986866641e-18</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.004999999999999542</v>
+        <v>0.005000000000000108</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.93310952988333e-16</v>
+        <v>1.609820512624577e-17</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -3035,7 +3035,7 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>3.902679479830532e-12</v>
+        <v>5.374947786592948e-13</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -3053,7 +3053,7 @@
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>-3.902679479830532e-12</v>
+        <v>-5.374947786592948e-13</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -3085,19 +3085,19 @@
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>-1.61907524424502e-13</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>-4.04768811061255e-11</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.93310952988333e-16</v>
+        <v>-1.609820512624577e-17</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002499999999999709</v>
+        <v>0.002500000000000045</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.004330127018921833</v>
+        <v>-0.004330127018922291</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -3109,13 +3109,13 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-6.656716817340045e-16</v>
+        <v>4.217979690080612e-17</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.662702988502231e-16</v>
+        <v>2.496555289566721e-17</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.005773502691895882</v>
+        <v>-0.005773502691896366</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -3127,13 +3127,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.004999999999999543</v>
+        <v>0.005000000000000108</v>
       </c>
       <c r="T4" t="n">
-        <v>-7.24247051220317e-17</v>
+        <v>-9.974659986866641e-18</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.93310952988333e-16</v>
+        <v>-1.609820512624577e-17</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -3145,13 +3145,13 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.004999999999999543</v>
+        <v>0.005000000000000106</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.002886751345948172</v>
+        <v>-0.002886751345948161</v>
       </c>
       <c r="AA4" t="n">
-        <v>-6.656716817340045e-16</v>
+        <v>4.217979690080612e-17</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -3163,7 +3163,7 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.70530256582424e-13</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -3181,7 +3181,7 @@
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>-1.70530256582424e-13</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -3213,19 +3213,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.705961688788196e-12</v>
+        <v>-6.309721314696069e-13</v>
       </c>
       <c r="F5" t="n">
-        <v>-4.264904221970491e-10</v>
+        <v>-1.577430328674017e-10</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.93310952988333e-16</v>
+        <v>-1.609820512624577e-17</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002499999999999709</v>
+        <v>0.002500000000000045</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.004330127018921833</v>
+        <v>-0.004330127018922291</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -3237,13 +3237,13 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-5.60108479708646e-16</v>
+        <v>-6.640573517909717e-17</v>
       </c>
       <c r="N5" t="n">
-        <v>0.004999999999999626</v>
+        <v>0.005000000000000042</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.008660254037843948</v>
+        <v>-0.008660254037844501</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-7.24247051220317e-17</v>
+        <v>-9.974659986866641e-18</v>
       </c>
       <c r="T5" t="n">
-        <v>0.004999999999999542</v>
+        <v>0.005000000000000108</v>
       </c>
       <c r="U5" t="n">
-        <v>1.93310952988333e-16</v>
+        <v>1.609820512624577e-17</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -3273,13 +3273,13 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-1.040834085586084e-16</v>
+        <v>-2.168404344971009e-17</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.009999999999999433</v>
+        <v>0.01000000000000012</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.60108479708646e-16</v>
+        <v>6.640573517909717e-17</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -3291,7 +3291,7 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.705961688788196e-12</v>
+        <v>6.30972131469607e-13</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>-1.705961688788196e-12</v>
+        <v>-6.30972131469607e-13</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -3341,19 +3341,19 @@
         <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>4.04768811061255e-14</v>
+        <v>1.214306433183765e-13</v>
       </c>
       <c r="F6" t="n">
-        <v>1.011922027653137e-11</v>
+        <v>3.035766082959412e-11</v>
       </c>
       <c r="G6" t="n">
-        <v>-6.656716817340045e-16</v>
+        <v>4.217979690080612e-17</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.662702988502231e-16</v>
+        <v>2.496555289566721e-17</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.005773502691895882</v>
+        <v>-0.005773502691896366</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -3365,13 +3365,13 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-5.60108479708646e-16</v>
+        <v>-6.640573517909717e-17</v>
       </c>
       <c r="N6" t="n">
-        <v>0.004999999999999626</v>
+        <v>0.005000000000000042</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.008660254037843948</v>
+        <v>-0.008660254037844501</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -3383,13 +3383,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.004999999999999808</v>
+        <v>-0.005000000000000082</v>
       </c>
       <c r="T6" t="n">
-        <v>0.00288675134594771</v>
+        <v>0.002886751345948204</v>
       </c>
       <c r="U6" t="n">
-        <v>6.656716817340045e-16</v>
+        <v>-4.217979690080612e-17</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -3401,13 +3401,13 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.004999999999999808</v>
+        <v>-0.005000000000000079</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.008660254037843844</v>
+        <v>0.00866025403784448</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.60108479708646e-16</v>
+        <v>6.640573517909717e-17</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -3419,7 +3419,7 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-2.842170943040401e-14</v>
+        <v>-1.13686837721616e-13</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3437,7 +3437,7 @@
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>1.13686837721616e-13</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -3469,19 +3469,19 @@
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>466.666666666658</v>
+        <v>466.6666666666679</v>
       </c>
       <c r="F7" t="n">
-        <v>116666.6666666645</v>
+        <v>116666.666666667</v>
       </c>
       <c r="G7" t="n">
-        <v>-6.656716817340045e-16</v>
+        <v>4.217979690080612e-17</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.662702988502231e-16</v>
+        <v>2.496555289566721e-17</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.005773502691895882</v>
+        <v>-0.005773502691896366</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -3493,13 +3493,13 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01999999999999778</v>
+        <v>0.02000000000000019</v>
       </c>
       <c r="N7" t="n">
-        <v>0.009999999999999551</v>
+        <v>0.01000000000000005</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.005773502691895869</v>
+        <v>-0.005773502691896375</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -3511,13 +3511,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.662702988502231e-16</v>
+        <v>2.496555289566721e-17</v>
       </c>
       <c r="T7" t="n">
-        <v>6.656716817340045e-16</v>
+        <v>-4.217979690080612e-17</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.005773502691895882</v>
+        <v>-0.005773502691896366</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -3529,13 +3529,13 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.009999999999999551</v>
+        <v>0.01000000000000005</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.01999999999999778</v>
+        <v>-0.02000000000000019</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.005773502691895869</v>
+        <v>-0.005773502691896375</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -3547,7 +3547,7 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>8.412825991399586e-12</v>
+        <v>-1.4210854715202e-12</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>-8.412825991399586e-12</v>
+        <v>1.4210854715202e-12</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -3597,19 +3597,19 @@
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>3.23815048849004e-13</v>
+        <v>4.04768811061255e-13</v>
       </c>
       <c r="F8" t="n">
-        <v>8.095376221225099e-11</v>
+        <v>1.011922027653137e-10</v>
       </c>
       <c r="G8" t="n">
-        <v>-5.60108479708646e-16</v>
+        <v>-6.640573517909717e-17</v>
       </c>
       <c r="H8" t="n">
-        <v>0.004999999999999626</v>
+        <v>0.005000000000000042</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.008660254037843948</v>
+        <v>-0.008660254037844501</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -3621,13 +3621,13 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01999999999999778</v>
+        <v>0.02000000000000019</v>
       </c>
       <c r="N8" t="n">
-        <v>0.009999999999999551</v>
+        <v>0.01000000000000005</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.005773502691895869</v>
+        <v>-0.005773502691896375</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -3639,13 +3639,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.009999999999999433</v>
+        <v>0.01000000000000012</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.040834085586084e-16</v>
+        <v>-2.081668171172169e-17</v>
       </c>
       <c r="U8" t="n">
-        <v>-5.60108479708646e-16</v>
+        <v>-6.640573517909717e-17</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -3657,13 +3657,13 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.00999999999999944</v>
+        <v>0.01000000000000013</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.005773502691896063</v>
+        <v>0.005773502691896244</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01999999999999778</v>
+        <v>0.02000000000000019</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-3.410605131648481e-13</v>
+        <v>-3.979039320256561e-13</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3693,7 +3693,7 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.410605131648481e-13</v>
+        <v>3.979039320256561e-13</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -3725,19 +3725,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E9" t="n">
-        <v>7.478188224824971e-13</v>
+        <v>-6.54341469672185e-13</v>
       </c>
       <c r="F9" t="n">
-        <v>1.869547056206243e-10</v>
+        <v>-1.635853674180462e-10</v>
       </c>
       <c r="G9" t="n">
-        <v>-5.60108479708646e-16</v>
+        <v>-6.640573517909717e-17</v>
       </c>
       <c r="H9" t="n">
-        <v>0.004999999999999626</v>
+        <v>0.005000000000000042</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.008660254037843948</v>
+        <v>-0.008660254037844501</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -3749,13 +3749,13 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02999999999999752</v>
+        <v>0.03000000000000024</v>
       </c>
       <c r="N9" t="n">
-        <v>0.007499999999999598</v>
+        <v>0.007500000000000032</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.004330127018921832</v>
+        <v>-0.004330127018922303</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -3767,13 +3767,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.008660254037843844</v>
+        <v>0.00866025403784448</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.004999999999999807</v>
+        <v>-0.005000000000000077</v>
       </c>
       <c r="U9" t="n">
-        <v>-5.60108479708646e-16</v>
+        <v>-6.640573517909717e-17</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.008660254037843857</v>
+        <v>0.008660254037844468</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.118896642005041e-16</v>
+        <v>-7.849623728795052e-17</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.02999999999999752</v>
+        <v>0.03000000000000024</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -3803,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-7.389644451905042e-13</v>
+        <v>6.252776074688882e-13</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -3821,7 +3821,7 @@
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>7.389644451905042e-13</v>
+        <v>-6.252776074688882e-13</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -3853,19 +3853,19 @@
         <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>4.04768811061255e-14</v>
+        <v>-2.42861286636753e-13</v>
       </c>
       <c r="F10" t="n">
-        <v>1.011922027653137e-11</v>
+        <v>-6.071532165918825e-11</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01999999999999778</v>
+        <v>0.02000000000000019</v>
       </c>
       <c r="H10" t="n">
-        <v>0.009999999999999551</v>
+        <v>0.01000000000000005</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.005773502691895869</v>
+        <v>-0.005773502691896375</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -3877,13 +3877,13 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.02999999999999752</v>
+        <v>0.03000000000000024</v>
       </c>
       <c r="N10" t="n">
-        <v>0.007499999999999598</v>
+        <v>0.007500000000000032</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.004330127018921832</v>
+        <v>-0.004330127018922303</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>-7.632783294297951e-17</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01154700538379193</v>
+        <v>0.01154700538379262</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.01999999999999778</v>
+        <v>-0.02000000000000019</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -3913,13 +3913,13 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.114559833315099e-16</v>
+        <v>-7.892991815694472e-17</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.008660254037843859</v>
+        <v>0.00866025403784447</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.02999999999999752</v>
+        <v>-0.03000000000000024</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -3931,7 +3931,7 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-4.047688110612496e-14</v>
+        <v>2.42861286636753e-13</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -3949,7 +3949,7 @@
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>4.047688110612496e-14</v>
+        <v>-2.42861286636753e-13</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -3981,19 +3981,19 @@
         <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.533410683886055e-12</v>
+        <v>1.295260195396016e-12</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.133352670971514e-09</v>
+        <v>3.23815048849004e-10</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01999999999999778</v>
+        <v>0.02000000000000019</v>
       </c>
       <c r="H11" t="n">
-        <v>0.009999999999999551</v>
+        <v>0.01000000000000005</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.005773502691895869</v>
+        <v>-0.005773502691896375</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -4005,10 +4005,10 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.05999999999999572</v>
+        <v>0.0600000000000005</v>
       </c>
       <c r="N11" t="n">
-        <v>0.009999999999999454</v>
+        <v>0.01000000000000008</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -4023,13 +4023,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.009999999999999551</v>
+        <v>0.01000000000000005</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.01999999999999778</v>
+        <v>-0.02000000000000019</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.005773502691895869</v>
+        <v>-0.005773502691896375</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -4041,10 +4041,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.009999999999999454</v>
+        <v>0.01000000000000008</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.05999999999999572</v>
+        <v>-0.0600000000000005</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -4059,7 +4059,7 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>4.547473508864641e-12</v>
+        <v>-1.250555214937776e-12</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -4077,7 +4077,7 @@
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>-4.547473508864641e-12</v>
+        <v>1.250555214937776e-12</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -4109,19 +4109,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E12" t="n">
-        <v>2.991275289929988e-12</v>
+        <v>-6.54341469672185e-13</v>
       </c>
       <c r="F12" t="n">
-        <v>7.47818822482497e-10</v>
+        <v>-1.635853674180462e-10</v>
       </c>
       <c r="G12" t="n">
-        <v>0.02999999999999752</v>
+        <v>0.03000000000000024</v>
       </c>
       <c r="H12" t="n">
-        <v>0.007499999999999598</v>
+        <v>0.007500000000000032</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.004330127018921832</v>
+        <v>-0.004330127018922303</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -4133,10 +4133,10 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.05999999999999572</v>
+        <v>0.0600000000000005</v>
       </c>
       <c r="N12" t="n">
-        <v>0.009999999999999454</v>
+        <v>0.01000000000000008</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -4151,13 +4151,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.008660254037843857</v>
+        <v>0.008660254037844468</v>
       </c>
       <c r="T12" t="n">
-        <v>1.118896642005041e-16</v>
+        <v>-7.849623728795052e-17</v>
       </c>
       <c r="U12" t="n">
-        <v>0.02999999999999752</v>
+        <v>0.03000000000000024</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -4169,13 +4169,13 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.008660254037843913</v>
+        <v>0.008660254037844456</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.004999999999999727</v>
+        <v>0.00500000000000004</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.05999999999999572</v>
+        <v>0.0600000000000005</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -4187,7 +4187,7 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-3.012701199622825e-12</v>
+        <v>6.821210263296962e-13</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -4205,7 +4205,7 @@
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.012701199622825e-12</v>
+        <v>-6.821210263296962e-13</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -4237,13 +4237,13 @@
         <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>1.238837225825222e-11</v>
+        <v>-1.267399679064165e-12</v>
       </c>
       <c r="F13" t="n">
-        <v>3.097093064563055e-09</v>
+        <v>-3.168499197660412e-10</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.676274217120448e-17</v>
+        <v>-4.340689376152277e-19</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -4261,13 +4261,13 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-6.6479308875418e-16</v>
+        <v>4.237319201299675e-17</v>
       </c>
       <c r="N13" t="n">
-        <v>2.654651198196905e-16</v>
+        <v>-2.715856455137496e-17</v>
       </c>
       <c r="O13" t="n">
-        <v>0.005773502691895886</v>
+        <v>0.00577350269189637</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -4282,7 +4282,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.676274217120448e-17</v>
+        <v>4.340689376152277e-19</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -4297,13 +4297,13 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.654651198196905e-16</v>
+        <v>-2.715856455137496e-17</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.6479308875418e-16</v>
+        <v>-4.237319201299675e-17</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.005773502691895886</v>
+        <v>0.00577350269189637</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-1.238837225825223e-11</v>
+        <v>1.267399679064165e-12</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -4333,7 +4333,7 @@
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.238837225825223e-11</v>
+        <v>-1.267399679064165e-12</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -4365,13 +4365,13 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E14" t="n">
-        <v>4.089634185451156e-12</v>
+        <v>4.907561022541388e-13</v>
       </c>
       <c r="F14" t="n">
-        <v>1.022408546362789e-09</v>
+        <v>1.226890255635347e-10</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.676274217120448e-17</v>
+        <v>-4.340689376152277e-19</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -4389,13 +4389,13 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.925891125394515e-16</v>
+        <v>-1.58091034875743e-17</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.002499999999999708</v>
+        <v>-0.002500000000000048</v>
       </c>
       <c r="O14" t="n">
-        <v>0.004330127018921839</v>
+        <v>0.004330127018922295</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -4413,7 +4413,7 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.676274217120448e-17</v>
+        <v>4.340689376152277e-19</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -4425,13 +4425,13 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>7.589415207398531e-17</v>
+        <v>9.107298248878237e-18</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0.004999999999999546</v>
+        <v>-0.005000000000000112</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.925891125394515e-16</v>
+        <v>1.58091034875743e-17</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -4443,7 +4443,7 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>-4.089634185451156e-12</v>
+        <v>-4.907561022541388e-13</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -4461,7 +4461,7 @@
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>4.089634185451156e-12</v>
+        <v>4.907561022541388e-13</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -4493,19 +4493,19 @@
         <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>1.61907524424502e-13</v>
+        <v>8.095376221225099e-14</v>
       </c>
       <c r="F15" t="n">
-        <v>4.04768811061255e-11</v>
+        <v>2.023844055306275e-11</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.925891125394515e-16</v>
+        <v>-1.58091034875743e-17</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.002499999999999708</v>
+        <v>-0.002500000000000048</v>
       </c>
       <c r="I15" t="n">
-        <v>0.004330127018921839</v>
+        <v>0.004330127018922295</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -4517,13 +4517,13 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-6.6479308875418e-16</v>
+        <v>4.237319201299675e-17</v>
       </c>
       <c r="N15" t="n">
-        <v>2.654651198196905e-16</v>
+        <v>-2.715856455137496e-17</v>
       </c>
       <c r="O15" t="n">
-        <v>0.005773502691895886</v>
+        <v>0.00577350269189637</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -4535,13 +4535,13 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.004999999999999547</v>
+        <v>-0.005000000000000112</v>
       </c>
       <c r="T15" t="n">
-        <v>7.546047120499111e-17</v>
+        <v>8.673617379884035e-18</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.925891125394515e-16</v>
+        <v>-1.58091034875743e-17</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -4553,13 +4553,13 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.004999999999999546</v>
+        <v>-0.005000000000000111</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.002886751345948173</v>
+        <v>0.002886751345948162</v>
       </c>
       <c r="AA15" t="n">
-        <v>-6.6479308875418e-16</v>
+        <v>4.237319201299675e-17</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -4571,7 +4571,7 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>-1.70530256582424e-13</v>
+        <v>-1.13686837721616e-13</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -4589,7 +4589,7 @@
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.70530256582424e-13</v>
+        <v>1.13686837721616e-13</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -4621,19 +4621,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E16" t="n">
-        <v>1.65922301238304e-12</v>
+        <v>5.374947786592948e-13</v>
       </c>
       <c r="F16" t="n">
-        <v>4.148057530957601e-10</v>
+        <v>1.343736946648237e-10</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.925891125394515e-16</v>
+        <v>-1.58091034875743e-17</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.002499999999999708</v>
+        <v>-0.002500000000000048</v>
       </c>
       <c r="I16" t="n">
-        <v>0.004330127018921839</v>
+        <v>0.004330127018922295</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -4645,13 +4645,13 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-5.600381307339044e-16</v>
+        <v>-6.63157692652396e-17</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.004999999999999622</v>
+        <v>-0.005000000000000043</v>
       </c>
       <c r="O16" t="n">
-        <v>0.008660254037843944</v>
+        <v>0.008660254037844498</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -4663,13 +4663,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>7.589415207398531e-17</v>
+        <v>9.107298248878237e-18</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.004999999999999546</v>
+        <v>-0.005000000000000112</v>
       </c>
       <c r="U16" t="n">
-        <v>1.925891125394515e-16</v>
+        <v>1.58091034875743e-17</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -4681,13 +4681,13 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.066854937725736e-16</v>
+        <v>1.908195823574488e-17</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0.009999999999999428</v>
+        <v>-0.01000000000000012</v>
       </c>
       <c r="AA16" t="n">
-        <v>5.600381307339044e-16</v>
+        <v>6.63157692652396e-17</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -4699,7 +4699,7 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>-1.65922301238304e-12</v>
+        <v>-5.374947786592948e-13</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -4717,7 +4717,7 @@
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.65922301238304e-12</v>
+        <v>5.374947786592948e-13</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -4749,19 +4749,19 @@
         <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.023844055306275e-13</v>
+        <v>-3.642919299551295e-13</v>
       </c>
       <c r="F17" t="n">
-        <v>-5.059610138265687e-11</v>
+        <v>-9.107298248878237e-11</v>
       </c>
       <c r="G17" t="n">
-        <v>-6.6479308875418e-16</v>
+        <v>4.237319201299675e-17</v>
       </c>
       <c r="H17" t="n">
-        <v>2.654651198196905e-16</v>
+        <v>-2.715856455137496e-17</v>
       </c>
       <c r="I17" t="n">
-        <v>0.005773502691895886</v>
+        <v>0.00577350269189637</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -4773,13 +4773,13 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-5.600381307339044e-16</v>
+        <v>-6.63157692652396e-17</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.004999999999999622</v>
+        <v>-0.005000000000000043</v>
       </c>
       <c r="O17" t="n">
-        <v>0.008660254037843944</v>
+        <v>0.008660254037844498</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -4791,13 +4791,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.004999999999999811</v>
+        <v>0.005000000000000083</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.002886751345947713</v>
+        <v>-0.002886751345948208</v>
       </c>
       <c r="U17" t="n">
-        <v>6.6479308875418e-16</v>
+        <v>-4.237319201299675e-17</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -4809,13 +4809,13 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.004999999999999807</v>
+        <v>0.005000000000000076</v>
       </c>
       <c r="Z17" t="n">
-        <v>-0.008660254037843838</v>
+        <v>-0.00866025403784448</v>
       </c>
       <c r="AA17" t="n">
-        <v>5.600381307339044e-16</v>
+        <v>6.63157692652396e-17</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -4827,7 +4827,7 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.273736754432321e-13</v>
+        <v>3.694822225952521e-13</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -4845,7 +4845,7 @@
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>-2.273736754432321e-13</v>
+        <v>-3.694822225952521e-13</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -4877,19 +4877,19 @@
         <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>-466.6666666666582</v>
+        <v>-466.6666666666679</v>
       </c>
       <c r="F18" t="n">
-        <v>-116666.6666666645</v>
+        <v>-116666.666666667</v>
       </c>
       <c r="G18" t="n">
-        <v>-6.6479308875418e-16</v>
+        <v>4.237319201299675e-17</v>
       </c>
       <c r="H18" t="n">
-        <v>2.654651198196905e-16</v>
+        <v>-2.715856455137496e-17</v>
       </c>
       <c r="I18" t="n">
-        <v>0.005773502691895886</v>
+        <v>0.00577350269189637</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -4901,13 +4901,13 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.01999999999999778</v>
+        <v>0.02000000000000019</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.009999999999999554</v>
+        <v>-0.01000000000000005</v>
       </c>
       <c r="O18" t="n">
-        <v>0.005773502691895859</v>
+        <v>0.005773502691896366</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -4919,13 +4919,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.654651198196905e-16</v>
+        <v>-2.715856455137496e-17</v>
       </c>
       <c r="T18" t="n">
-        <v>6.6479308875418e-16</v>
+        <v>-4.237319201299675e-17</v>
       </c>
       <c r="U18" t="n">
-        <v>0.005773502691895886</v>
+        <v>0.00577350269189637</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -4937,13 +4937,13 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>-0.009999999999999554</v>
+        <v>-0.01000000000000005</v>
       </c>
       <c r="Z18" t="n">
-        <v>-0.01999999999999778</v>
+        <v>-0.02000000000000019</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.005773502691895859</v>
+        <v>0.005773502691896366</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -4955,7 +4955,7 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>-8.29913915367797e-12</v>
+        <v>1.364242052659392e-12</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -4973,7 +4973,7 @@
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>8.29913915367797e-12</v>
+        <v>-1.364242052659392e-12</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -5005,19 +5005,19 @@
         <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.42861286636753e-13</v>
+        <v>-8.095376221225099e-14</v>
       </c>
       <c r="F19" t="n">
-        <v>-6.071532165918825e-11</v>
+        <v>-2.023844055306275e-11</v>
       </c>
       <c r="G19" t="n">
-        <v>-5.600381307339044e-16</v>
+        <v>-6.63157692652396e-17</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.004999999999999622</v>
+        <v>-0.005000000000000043</v>
       </c>
       <c r="I19" t="n">
-        <v>0.008660254037843944</v>
+        <v>0.008660254037844498</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -5029,13 +5029,13 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.01999999999999778</v>
+        <v>0.02000000000000019</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.009999999999999554</v>
+        <v>-0.01000000000000005</v>
       </c>
       <c r="O19" t="n">
-        <v>0.005773502691895859</v>
+        <v>0.005773502691896366</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -5047,13 +5047,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.009999999999999428</v>
+        <v>-0.01000000000000012</v>
       </c>
       <c r="T19" t="n">
-        <v>1.058181320345852e-16</v>
+        <v>1.821459649775647e-17</v>
       </c>
       <c r="U19" t="n">
-        <v>-5.600381307339044e-16</v>
+        <v>-6.63157692652396e-17</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -5065,13 +5065,13 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>-0.009999999999999433</v>
+        <v>-0.01000000000000012</v>
       </c>
       <c r="Z19" t="n">
-        <v>-0.005773502691896071</v>
+        <v>-0.00577350269189625</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.01999999999999778</v>
+        <v>0.02000000000000019</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -5083,7 +5083,7 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.273736754432321e-13</v>
+        <v>5.684341886080801e-14</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -5101,7 +5101,7 @@
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>-2.273736754432321e-13</v>
+        <v>-5.684341886080801e-14</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -5133,19 +5133,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E20" t="n">
-        <v>-7.478188224824971e-13</v>
+        <v>6.54341469672185e-13</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.869547056206243e-10</v>
+        <v>1.635853674180462e-10</v>
       </c>
       <c r="G20" t="n">
-        <v>-5.600381307339044e-16</v>
+        <v>-6.63157692652396e-17</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.004999999999999622</v>
+        <v>-0.005000000000000043</v>
       </c>
       <c r="I20" t="n">
-        <v>0.008660254037843944</v>
+        <v>0.008660254037844498</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -5157,13 +5157,13 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.02999999999999752</v>
+        <v>0.03000000000000023</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.007499999999999597</v>
+        <v>-0.007500000000000036</v>
       </c>
       <c r="O20" t="n">
-        <v>0.004330127018921823</v>
+        <v>0.004330127018922292</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -5175,13 +5175,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.008660254037843838</v>
+        <v>-0.008660254037844478</v>
       </c>
       <c r="T20" t="n">
-        <v>0.004999999999999805</v>
+        <v>0.005000000000000075</v>
       </c>
       <c r="U20" t="n">
-        <v>-5.600381307339044e-16</v>
+        <v>-6.63157692652396e-17</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -5193,13 +5193,13 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>-0.008660254037843852</v>
+        <v>-0.008660254037844466</v>
       </c>
       <c r="Z20" t="n">
-        <v>-1.196959198423997e-16</v>
+        <v>6.722053469410127e-17</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.02999999999999752</v>
+        <v>0.03000000000000023</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -5211,7 +5211,7 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>7.389644451905042e-13</v>
+        <v>-6.821210263296962e-13</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -5229,7 +5229,7 @@
         <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>-7.389644451905042e-13</v>
+        <v>6.821210263296962e-13</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -5261,19 +5261,19 @@
         <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>2.833381677428785e-13</v>
+        <v>8.095376221225099e-14</v>
       </c>
       <c r="F21" t="n">
-        <v>7.083454193571961e-11</v>
+        <v>2.023844055306275e-11</v>
       </c>
       <c r="G21" t="n">
-        <v>0.01999999999999778</v>
+        <v>0.02000000000000019</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.009999999999999554</v>
+        <v>-0.01000000000000005</v>
       </c>
       <c r="I21" t="n">
-        <v>0.005773502691895859</v>
+        <v>0.005773502691896366</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -5285,13 +5285,13 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.02999999999999752</v>
+        <v>0.03000000000000023</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.007499999999999597</v>
+        <v>-0.007500000000000036</v>
       </c>
       <c r="O21" t="n">
-        <v>0.004330127018921823</v>
+        <v>0.004330127018922292</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -5303,13 +5303,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.222980050563649e-16</v>
+        <v>6.678685382510707e-17</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.01154700538379193</v>
+        <v>-0.01154700538379262</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.01999999999999778</v>
+        <v>-0.02000000000000019</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -5321,13 +5321,13 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>-1.192622389734055e-16</v>
+        <v>6.765421556309548e-17</v>
       </c>
       <c r="Z21" t="n">
-        <v>-0.008660254037843852</v>
+        <v>-0.008660254037844468</v>
       </c>
       <c r="AA21" t="n">
-        <v>-0.02999999999999752</v>
+        <v>-0.03000000000000023</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -5339,7 +5339,7 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>-2.833381677428796e-13</v>
+        <v>-8.095376221225073e-14</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.833381677428796e-13</v>
+        <v>8.095376221225073e-14</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -5389,19 +5389,19 @@
         <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>4.776271970522808e-12</v>
+        <v>-1.376213957608267e-12</v>
       </c>
       <c r="F22" t="n">
-        <v>1.194067992630702e-09</v>
+        <v>-3.440534894020667e-10</v>
       </c>
       <c r="G22" t="n">
-        <v>0.01999999999999778</v>
+        <v>0.02000000000000019</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.009999999999999554</v>
+        <v>-0.01000000000000005</v>
       </c>
       <c r="I22" t="n">
-        <v>0.005773502691895859</v>
+        <v>0.005773502691896366</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -5413,10 +5413,10 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.05999999999999572</v>
+        <v>0.0600000000000005</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.009999999999999452</v>
+        <v>-0.01000000000000008</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -5431,13 +5431,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.009999999999999554</v>
+        <v>-0.01000000000000005</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.01999999999999778</v>
+        <v>-0.02000000000000019</v>
       </c>
       <c r="U22" t="n">
-        <v>0.005773502691895859</v>
+        <v>0.005773502691896366</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -5449,10 +5449,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>-0.009999999999999452</v>
+        <v>-0.01000000000000008</v>
       </c>
       <c r="Z22" t="n">
-        <v>-0.05999999999999572</v>
+        <v>-0.0600000000000005</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>-4.774847184307873e-12</v>
+        <v>1.364242052659392e-12</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -5485,7 +5485,7 @@
         <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>4.774847184307873e-12</v>
+        <v>-1.364242052659392e-12</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -5517,19 +5517,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.178229995550613e-12</v>
+        <v>4.673867640515606e-13</v>
       </c>
       <c r="F23" t="n">
-        <v>-7.945574988876531e-10</v>
+        <v>1.168466910128902e-10</v>
       </c>
       <c r="G23" t="n">
-        <v>0.02999999999999752</v>
+        <v>0.03000000000000023</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.007499999999999597</v>
+        <v>-0.007500000000000036</v>
       </c>
       <c r="I23" t="n">
-        <v>0.004330127018921823</v>
+        <v>0.004330127018922292</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -5541,10 +5541,10 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.05999999999999572</v>
+        <v>0.0600000000000005</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.009999999999999452</v>
+        <v>-0.01000000000000008</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -5559,13 +5559,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.008660254037843852</v>
+        <v>-0.008660254037844466</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.196959198423997e-16</v>
+        <v>6.722053469410127e-17</v>
       </c>
       <c r="U23" t="n">
-        <v>0.02999999999999752</v>
+        <v>0.03000000000000023</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -5577,13 +5577,13 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>-0.008660254037843911</v>
+        <v>-0.008660254037844458</v>
       </c>
       <c r="Z23" t="n">
-        <v>-0.004999999999999726</v>
+        <v>-0.005000000000000042</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.05999999999999572</v>
+        <v>0.0600000000000005</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -5595,7 +5595,7 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>3.183231456205249e-12</v>
+        <v>-4.547473508864641e-13</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -5613,7 +5613,7 @@
         <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>-3.183231456205249e-12</v>
+        <v>4.547473508864641e-13</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -5645,10 +5645,10 @@
         <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.564522602645751e-12</v>
+        <v>-4.051310084408792e-14</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.911306506614377e-10</v>
+        <v>-1.012827521102198e-11</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -5669,7 +5669,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.676274217120448e-17</v>
+        <v>-4.340689376152277e-19</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>-1.676274217120448e-17</v>
+        <v>-4.340689376152277e-19</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -5723,7 +5723,7 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.564522602645751e-12</v>
+        <v>4.051310084408793e-14</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -5741,7 +5741,7 @@
         <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>-1.564522602645751e-12</v>
+        <v>-4.051310084408793e-14</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -5773,19 +5773,19 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>6.7371775228936e-14</v>
+        <v>2.698281960933733e-14</v>
       </c>
       <c r="F25" t="n">
-        <v>1.6842943807234e-11</v>
+        <v>6.745704902334333e-12</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.93310952988333e-16</v>
+        <v>-1.609820512624577e-17</v>
       </c>
       <c r="H25" t="n">
-        <v>0.002499999999999709</v>
+        <v>0.002500000000000045</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.004330127018921833</v>
+        <v>-0.004330127018922291</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -5797,13 +5797,13 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.925891125394515e-16</v>
+        <v>-1.58091034875743e-17</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.002499999999999708</v>
+        <v>-0.002500000000000048</v>
       </c>
       <c r="O25" t="n">
-        <v>0.004330127018921839</v>
+        <v>0.004330127018922295</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -5815,13 +5815,13 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.93310952988333e-16</v>
+        <v>-1.609820512624577e-17</v>
       </c>
       <c r="T25" t="n">
-        <v>0.002499999999999709</v>
+        <v>0.002500000000000045</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.004330127018921833</v>
+        <v>-0.004330127018922291</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -5833,13 +5833,13 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>-1.925891125394515e-16</v>
+        <v>-1.58091034875743e-17</v>
       </c>
       <c r="Z25" t="n">
-        <v>-0.002499999999999708</v>
+        <v>-0.002500000000000048</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.004330127018921839</v>
+        <v>0.004330127018922295</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -5851,7 +5851,7 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>-6.737177522893694e-14</v>
+        <v>-2.698281960933742e-14</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -5869,7 +5869,7 @@
         <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>6.737177522893694e-14</v>
+        <v>2.698281960933742e-14</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -5901,19 +5901,19 @@
         <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>8.200201145028953e-14</v>
+        <v>1.805021047112535e-14</v>
       </c>
       <c r="F26" t="n">
-        <v>2.050050286257238e-11</v>
+        <v>4.512552617781336e-12</v>
       </c>
       <c r="G26" t="n">
-        <v>-6.656716817340045e-16</v>
+        <v>4.217979690080612e-17</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.662702988502231e-16</v>
+        <v>2.496555289566721e-17</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.005773502691895882</v>
+        <v>-0.005773502691896366</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -5925,13 +5925,13 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-6.6479308875418e-16</v>
+        <v>4.237319201299675e-17</v>
       </c>
       <c r="N26" t="n">
-        <v>2.654651198196905e-16</v>
+        <v>-2.715856455137496e-17</v>
       </c>
       <c r="O26" t="n">
-        <v>0.005773502691895886</v>
+        <v>0.00577350269189637</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -5943,13 +5943,13 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>-6.656716817340045e-16</v>
+        <v>4.217979690080612e-17</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.662702988502231e-16</v>
+        <v>2.496555289566721e-17</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.005773502691895882</v>
+        <v>-0.005773502691896366</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -5961,13 +5961,13 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>-6.6479308875418e-16</v>
+        <v>4.237319201299675e-17</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.654651198196905e-16</v>
+        <v>-2.715856455137496e-17</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.005773502691895886</v>
+        <v>0.00577350269189637</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -5979,7 +5979,7 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>-8.200201145029306e-14</v>
+        <v>-1.805021047112511e-14</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
@@ -5997,7 +5997,7 @@
         <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>8.200201145029306e-14</v>
+        <v>1.805021047112511e-14</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -6029,19 +6029,19 @@
         <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>6.565904309215647e-15</v>
+        <v>8.39681862670618e-15</v>
       </c>
       <c r="F27" t="n">
-        <v>1.641476077303912e-12</v>
+        <v>2.099204656676545e-12</v>
       </c>
       <c r="G27" t="n">
-        <v>-5.60108479708646e-16</v>
+        <v>-6.640573517909717e-17</v>
       </c>
       <c r="H27" t="n">
-        <v>0.004999999999999626</v>
+        <v>0.005000000000000042</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.008660254037843948</v>
+        <v>-0.008660254037844501</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -6053,13 +6053,13 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-5.600381307339044e-16</v>
+        <v>-6.63157692652396e-17</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.004999999999999622</v>
+        <v>-0.005000000000000043</v>
       </c>
       <c r="O27" t="n">
-        <v>0.008660254037843944</v>
+        <v>0.008660254037844498</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -6071,13 +6071,13 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>-5.60108479708646e-16</v>
+        <v>-6.640573517909717e-17</v>
       </c>
       <c r="T27" t="n">
-        <v>0.004999999999999626</v>
+        <v>0.005000000000000042</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.008660254037843948</v>
+        <v>-0.008660254037844501</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -6089,13 +6089,13 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>-5.600381307339044e-16</v>
+        <v>-6.63157692652396e-17</v>
       </c>
       <c r="Z27" t="n">
-        <v>-0.004999999999999622</v>
+        <v>-0.005000000000000043</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.008660254037843944</v>
+        <v>0.008660254037844498</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -6107,7 +6107,7 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>-6.565904309210424e-15</v>
+        <v>-8.396818626705484e-15</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
@@ -6125,7 +6125,7 @@
         <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>6.565904309210424e-15</v>
+        <v>8.396818626705484e-15</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -6163,13 +6163,13 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.01999999999999778</v>
+        <v>0.02000000000000019</v>
       </c>
       <c r="H28" t="n">
-        <v>0.009999999999999551</v>
+        <v>0.01000000000000005</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.005773502691895869</v>
+        <v>-0.005773502691896375</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -6181,13 +6181,13 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.01999999999999778</v>
+        <v>0.02000000000000019</v>
       </c>
       <c r="N28" t="n">
-        <v>-0.009999999999999554</v>
+        <v>-0.01000000000000005</v>
       </c>
       <c r="O28" t="n">
-        <v>0.005773502691895859</v>
+        <v>0.005773502691896366</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -6199,13 +6199,13 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.01999999999999778</v>
+        <v>0.02000000000000019</v>
       </c>
       <c r="T28" t="n">
-        <v>0.009999999999999551</v>
+        <v>0.01000000000000005</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.005773502691895869</v>
+        <v>-0.005773502691896375</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -6217,13 +6217,13 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.01999999999999778</v>
+        <v>0.02000000000000019</v>
       </c>
       <c r="Z28" t="n">
-        <v>-0.009999999999999554</v>
+        <v>-0.01000000000000005</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.005773502691895859</v>
+        <v>0.005773502691896366</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -6291,13 +6291,13 @@
         <v>-8.095376221225099e-11</v>
       </c>
       <c r="G29" t="n">
-        <v>0.02999999999999752</v>
+        <v>0.03000000000000024</v>
       </c>
       <c r="H29" t="n">
-        <v>0.007499999999999598</v>
+        <v>0.007500000000000032</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.004330127018921832</v>
+        <v>-0.004330127018922303</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -6309,13 +6309,13 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.02999999999999752</v>
+        <v>0.03000000000000023</v>
       </c>
       <c r="N29" t="n">
-        <v>-0.007499999999999597</v>
+        <v>-0.007500000000000036</v>
       </c>
       <c r="O29" t="n">
-        <v>0.004330127018921823</v>
+        <v>0.004330127018922292</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
@@ -6327,13 +6327,13 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0.02999999999999752</v>
+        <v>0.03000000000000024</v>
       </c>
       <c r="T29" t="n">
-        <v>0.007499999999999598</v>
+        <v>0.007500000000000032</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.004330127018921832</v>
+        <v>-0.004330127018922303</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -6345,13 +6345,13 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.02999999999999752</v>
+        <v>0.03000000000000023</v>
       </c>
       <c r="Z29" t="n">
-        <v>-0.007499999999999597</v>
+        <v>-0.007500000000000036</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.004330127018921823</v>
+        <v>0.004330127018922292</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -6413,16 +6413,16 @@
         <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>6.476300976980079e-13</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>1.61907524424502e-10</v>
       </c>
       <c r="G30" t="n">
-        <v>0.05999999999999572</v>
+        <v>0.0600000000000005</v>
       </c>
       <c r="H30" t="n">
-        <v>0.009999999999999454</v>
+        <v>0.01000000000000008</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -6437,10 +6437,10 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.05999999999999572</v>
+        <v>0.0600000000000005</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.009999999999999452</v>
+        <v>-0.01000000000000008</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -6455,10 +6455,10 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0.05999999999999572</v>
+        <v>0.0600000000000005</v>
       </c>
       <c r="T30" t="n">
-        <v>0.009999999999999454</v>
+        <v>0.01000000000000008</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -6473,10 +6473,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.05999999999999572</v>
+        <v>0.0600000000000005</v>
       </c>
       <c r="Z30" t="n">
-        <v>-0.009999999999999452</v>
+        <v>-0.01000000000000008</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -6541,10 +6541,10 @@
         <v>6</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.426810058990924e-12</v>
+        <v>1.011922027653137e-14</v>
       </c>
       <c r="F31" t="n">
-        <v>-3.56702514747731e-10</v>
+        <v>2.529805069132844e-12</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -6565,13 +6565,13 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-1.925891125394515e-16</v>
+        <v>-1.58091034875743e-17</v>
       </c>
       <c r="N31" t="n">
-        <v>-0.002499999999999708</v>
+        <v>-0.002500000000000048</v>
       </c>
       <c r="O31" t="n">
-        <v>0.004330127018921839</v>
+        <v>0.004330127018922295</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
@@ -6601,13 +6601,13 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>-3.057450126409123e-17</v>
+        <v>2.168404344971009e-19</v>
       </c>
       <c r="Z31" t="n">
-        <v>-0.003779644730091796</v>
+        <v>-0.003779644730092345</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.003273268353539744</v>
+        <v>0.003273268353539973</v>
       </c>
       <c r="AB31" t="n">
         <v>0</v>
@@ -6619,7 +6619,7 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.426810058990924e-12</v>
+        <v>-1.011922027653138e-14</v>
       </c>
       <c r="AF31" t="n">
         <v>0</v>
@@ -6637,7 +6637,7 @@
         <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>-1.426810058990924e-12</v>
+        <v>1.011922027653138e-14</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -6669,13 +6669,13 @@
         <v>6</v>
       </c>
       <c r="E32" t="n">
-        <v>1.187467712477457e-12</v>
+        <v>-5.060515631714747e-14</v>
       </c>
       <c r="F32" t="n">
-        <v>2.968669281193641e-10</v>
+        <v>-1.265128907928687e-11</v>
       </c>
       <c r="G32" t="n">
-        <v>-1.676274217120448e-17</v>
+        <v>-4.340689376152277e-19</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -6693,13 +6693,13 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-1.93310952988333e-16</v>
+        <v>-1.609820512624577e-17</v>
       </c>
       <c r="N32" t="n">
-        <v>0.002499999999999709</v>
+        <v>0.002500000000000045</v>
       </c>
       <c r="O32" t="n">
-        <v>-0.004330127018921833</v>
+        <v>-0.004330127018922291</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
@@ -6711,13 +6711,13 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>8.381371085602238e-18</v>
+        <v>2.170344688076139e-19</v>
       </c>
       <c r="T32" t="n">
-        <v>-9.503581516393274e-18</v>
+        <v>-2.46093955883122e-19</v>
       </c>
       <c r="U32" t="n">
-        <v>1.097379069351042e-17</v>
+        <v>2.841648233501208e-19</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -6729,13 +6729,13 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>3.382710778154774e-17</v>
+        <v>-8.673617379884035e-19</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.003779644730091793</v>
+        <v>0.003779644730092341</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.00327326835353974</v>
+        <v>0.00327326835353997</v>
       </c>
       <c r="AB32" t="n">
         <v>0</v>
@@ -6747,7 +6747,7 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>-1.187467712477457e-12</v>
+        <v>5.060515631714749e-14</v>
       </c>
       <c r="AF32" t="n">
         <v>0</v>
@@ -6765,7 +6765,7 @@
         <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.187467712477457e-12</v>
+        <v>-5.060515631714749e-14</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -6797,10 +6797,10 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E33" t="n">
-        <v>-2.498773183476249e-12</v>
+        <v>-2.229534923420594e-13</v>
       </c>
       <c r="F33" t="n">
-        <v>-6.246932958690621e-10</v>
+        <v>-5.573837308551484e-11</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -6821,13 +6821,13 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-6.6479308875418e-16</v>
+        <v>4.237319201299675e-17</v>
       </c>
       <c r="N33" t="n">
-        <v>2.654651198196905e-16</v>
+        <v>-2.715856455137496e-17</v>
       </c>
       <c r="O33" t="n">
-        <v>0.005773502691895886</v>
+        <v>0.00577350269189637</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -6857,13 +6857,13 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>-5.986528605649763e-17</v>
+        <v>-5.341491050333823e-18</v>
       </c>
       <c r="Z33" t="n">
-        <v>7.133286256849499e-16</v>
+        <v>-5.004541440752285e-17</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.005773502691895886</v>
+        <v>0.00577350269189637</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
@@ -6875,7 +6875,7 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.498773183476248e-12</v>
+        <v>2.229534923420593e-13</v>
       </c>
       <c r="AF33" t="n">
         <v>0</v>
@@ -6893,7 +6893,7 @@
         <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>-2.498773183476248e-12</v>
+        <v>-2.229534923420593e-13</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -6925,13 +6925,13 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E34" t="n">
-        <v>2.172209048097271e-12</v>
+        <v>1.36588479121044e-13</v>
       </c>
       <c r="F34" t="n">
-        <v>5.430522620243177e-10</v>
+        <v>3.414711978026099e-11</v>
       </c>
       <c r="G34" t="n">
-        <v>-1.676274217120448e-17</v>
+        <v>-4.340689376152277e-19</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -6949,13 +6949,13 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-6.656716817340045e-16</v>
+        <v>4.217979690080612e-17</v>
       </c>
       <c r="N34" t="n">
-        <v>-2.662702988502231e-16</v>
+        <v>2.496555289566721e-17</v>
       </c>
       <c r="O34" t="n">
-        <v>-0.005773502691895882</v>
+        <v>-0.005773502691896366</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
@@ -6967,10 +6967,10 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>7.496526196823125e-18</v>
+        <v>1.941215302857529e-19</v>
       </c>
       <c r="T34" t="n">
-        <v>-1.499305239364625e-17</v>
+        <v>-3.882430605715059e-19</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -6985,13 +6985,13 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>5.953803076345464e-17</v>
+        <v>3.46649071876395e-18</v>
       </c>
       <c r="Z34" t="n">
-        <v>-7.144745501451922e-16</v>
+        <v>4.889169193305069e-17</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.005773502691895882</v>
+        <v>0.005773502691896366</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
@@ -7003,7 +7003,7 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>-2.172209048097271e-12</v>
+        <v>-1.365884791210439e-13</v>
       </c>
       <c r="AF34" t="n">
         <v>0</v>
@@ -7021,7 +7021,7 @@
         <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.172209048097271e-12</v>
+        <v>1.365884791210439e-13</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -7053,19 +7053,19 @@
         <v>6</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.315498635949079e-12</v>
+        <v>2.023844055306275e-14</v>
       </c>
       <c r="F35" t="n">
-        <v>-3.288746589872696e-10</v>
+        <v>5.059610138265687e-12</v>
       </c>
       <c r="G35" t="n">
-        <v>-1.93310952988333e-16</v>
+        <v>-1.609820512624577e-17</v>
       </c>
       <c r="H35" t="n">
-        <v>0.002499999999999709</v>
+        <v>0.002500000000000045</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.004330127018921833</v>
+        <v>-0.004330127018922291</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -7077,13 +7077,13 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-5.600381307339044e-16</v>
+        <v>-6.63157692652396e-17</v>
       </c>
       <c r="N35" t="n">
-        <v>-0.004999999999999622</v>
+        <v>-0.005000000000000043</v>
       </c>
       <c r="O35" t="n">
-        <v>0.008660254037843944</v>
+        <v>0.008660254037844498</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -7095,13 +7095,13 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>-1.595945597898663e-16</v>
+        <v>-1.691355389077387e-17</v>
       </c>
       <c r="T35" t="n">
-        <v>0.003779644730092012</v>
+        <v>0.003779644730092359</v>
       </c>
       <c r="U35" t="n">
-        <v>-0.003273268353539487</v>
+        <v>-0.003273268353539949</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -7113,13 +7113,13 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>-1.877838162744894e-16</v>
+        <v>-1.647987302177967e-17</v>
       </c>
       <c r="Z35" t="n">
-        <v>-0.00755928946018376</v>
+        <v>-0.00755928946018459</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.006546536707079803</v>
+        <v>0.006546536707079898</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
@@ -7131,7 +7131,7 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.315498635949078e-12</v>
+        <v>-2.023844055306278e-14</v>
       </c>
       <c r="AF35" t="n">
         <v>0</v>
@@ -7149,7 +7149,7 @@
         <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>-1.315498635949078e-12</v>
+        <v>2.023844055306278e-14</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -7181,19 +7181,19 @@
         <v>6</v>
       </c>
       <c r="E36" t="n">
-        <v>1.285140975119484e-12</v>
+        <v>-5.059610138265687e-14</v>
       </c>
       <c r="F36" t="n">
-        <v>3.212852437798711e-10</v>
+        <v>-1.264902534566422e-11</v>
       </c>
       <c r="G36" t="n">
-        <v>-1.925891125394515e-16</v>
+        <v>-1.58091034875743e-17</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.002499999999999708</v>
+        <v>-0.002500000000000048</v>
       </c>
       <c r="I36" t="n">
-        <v>0.004330127018921839</v>
+        <v>0.004330127018922295</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -7205,13 +7205,13 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-5.60108479708646e-16</v>
+        <v>-6.640573517909717e-17</v>
       </c>
       <c r="N36" t="n">
-        <v>0.004999999999999626</v>
+        <v>0.005000000000000042</v>
       </c>
       <c r="O36" t="n">
-        <v>-0.008660254037843948</v>
+        <v>-0.008660254037844501</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
@@ -7223,13 +7223,13 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>1.619798045693344e-16</v>
+        <v>1.582935171828836e-17</v>
       </c>
       <c r="T36" t="n">
-        <v>-0.003779644730092014</v>
+        <v>-0.003779644730092363</v>
       </c>
       <c r="U36" t="n">
-        <v>-0.003273268353539491</v>
+        <v>-0.003273268353539952</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -7241,13 +7241,13 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.895185397504662e-16</v>
+        <v>1.474514954580286e-17</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.007559289460183765</v>
+        <v>0.007559289460184591</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.006546536707079806</v>
+        <v>0.006546536707079901</v>
       </c>
       <c r="AB36" t="n">
         <v>0</v>
@@ -7259,7 +7259,7 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>-1.285140975119486e-12</v>
+        <v>5.059610138265691e-14</v>
       </c>
       <c r="AF36" t="n">
         <v>0</v>
@@ -7277,7 +7277,7 @@
         <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.285140975119486e-12</v>
+        <v>-5.059610138265691e-14</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -7309,19 +7309,19 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E37" t="n">
-        <v>-2.396648962531799e-12</v>
+        <v>-1.264441019196233e-13</v>
       </c>
       <c r="F37" t="n">
-        <v>-5.991622406329497e-10</v>
+        <v>-3.161102547990584e-11</v>
       </c>
       <c r="G37" t="n">
-        <v>-6.656716817340045e-16</v>
+        <v>4.217979690080612e-17</v>
       </c>
       <c r="H37" t="n">
-        <v>-2.662702988502231e-16</v>
+        <v>2.496555289566721e-17</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.005773502691895882</v>
+        <v>-0.005773502691896366</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -7333,13 +7333,13 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.01999999999999778</v>
+        <v>0.02000000000000019</v>
       </c>
       <c r="N37" t="n">
-        <v>-0.009999999999999554</v>
+        <v>-0.01000000000000005</v>
       </c>
       <c r="O37" t="n">
-        <v>0.005773502691895859</v>
+        <v>0.005773502691896366</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
@@ -7351,13 +7351,13 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>-5.358568216580811e-16</v>
+        <v>4.119324797769893e-17</v>
       </c>
       <c r="T37" t="n">
-        <v>4.763151546978791e-16</v>
+        <v>-2.656182258481926e-17</v>
       </c>
       <c r="U37" t="n">
-        <v>-0.005773502691895882</v>
+        <v>-0.005773502691896366</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -7369,13 +7369,13 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>-5.93275428784068e-16</v>
+        <v>3.816391647148976e-17</v>
       </c>
       <c r="Z37" t="n">
-        <v>-0.02236067977499571</v>
+        <v>-0.02236067977499809</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.005773502691895859</v>
+        <v>0.005773502691896366</v>
       </c>
       <c r="AB37" t="n">
         <v>0</v>
@@ -7387,7 +7387,7 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.396648962531798e-12</v>
+        <v>1.264441019196232e-13</v>
       </c>
       <c r="AF37" t="n">
         <v>0</v>
@@ -7405,7 +7405,7 @@
         <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>-2.396648962531798e-12</v>
+        <v>-1.264441019196232e-13</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -7437,19 +7437,19 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E38" t="n">
-        <v>2.298294889688984e-12</v>
+        <v>1.395193330238924e-13</v>
       </c>
       <c r="F38" t="n">
-        <v>5.745737224222461e-10</v>
+        <v>3.48798332559731e-11</v>
       </c>
       <c r="G38" t="n">
-        <v>-6.6479308875418e-16</v>
+        <v>4.237319201299675e-17</v>
       </c>
       <c r="H38" t="n">
-        <v>2.654651198196905e-16</v>
+        <v>-2.715856455137496e-17</v>
       </c>
       <c r="I38" t="n">
-        <v>0.005773502691895886</v>
+        <v>0.00577350269189637</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -7461,13 +7461,13 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.01999999999999778</v>
+        <v>0.02000000000000019</v>
       </c>
       <c r="N38" t="n">
-        <v>0.009999999999999551</v>
+        <v>0.01000000000000005</v>
       </c>
       <c r="O38" t="n">
-        <v>-0.005773502691895869</v>
+        <v>-0.005773502691896375</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -7479,13 +7479,13 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>5.347437289140614e-16</v>
+        <v>-4.324122615621858e-17</v>
       </c>
       <c r="T38" t="n">
-        <v>-4.758894042561681e-16</v>
+        <v>2.575405580424665e-17</v>
       </c>
       <c r="U38" t="n">
-        <v>-0.005773502691895886</v>
+        <v>-0.00577350269189637</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -7497,13 +7497,13 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>5.898059818321144e-16</v>
+        <v>-3.989863994746656e-17</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.02236067977499571</v>
+        <v>0.02236067977499809</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.005773502691895869</v>
+        <v>0.005773502691896375</v>
       </c>
       <c r="AB38" t="n">
         <v>0</v>
@@ -7515,7 +7515,7 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>-2.298294889688983e-12</v>
+        <v>-1.395193330238923e-13</v>
       </c>
       <c r="AF38" t="n">
         <v>0</v>
@@ -7533,7 +7533,7 @@
         <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>2.298294889688983e-12</v>
+        <v>1.395193330238923e-13</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -7565,19 +7565,19 @@
         <v>6</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.376213957608267e-12</v>
+        <v>-4.04768811061255e-14</v>
       </c>
       <c r="F39" t="n">
-        <v>-3.440534894020667e-10</v>
+        <v>-1.011922027653137e-11</v>
       </c>
       <c r="G39" t="n">
-        <v>-5.60108479708646e-16</v>
+        <v>-6.640573517909717e-17</v>
       </c>
       <c r="H39" t="n">
-        <v>0.004999999999999626</v>
+        <v>0.005000000000000042</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.008660254037843948</v>
+        <v>-0.008660254037844501</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -7589,13 +7589,13 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.02999999999999752</v>
+        <v>0.03000000000000023</v>
       </c>
       <c r="N39" t="n">
-        <v>-0.007499999999999597</v>
+        <v>-0.007500000000000036</v>
       </c>
       <c r="O39" t="n">
-        <v>0.004330127018921823</v>
+        <v>0.004330127018922292</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
@@ -7607,13 +7607,13 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0.00749999999999925</v>
+        <v>0.007500000000000047</v>
       </c>
       <c r="T39" t="n">
-        <v>-0.0009449111825227826</v>
+        <v>-0.0009449111825230588</v>
       </c>
       <c r="U39" t="n">
-        <v>-0.006546536707079806</v>
+        <v>-0.006546536707079901</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -7625,13 +7625,13 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.007499999999999221</v>
+        <v>0.007500000000000047</v>
       </c>
       <c r="Z39" t="n">
-        <v>-0.01984313483298294</v>
+        <v>-0.01984313483298454</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.0229128784747773</v>
+        <v>0.02291287847477943</v>
       </c>
       <c r="AB39" t="n">
         <v>0</v>
@@ -7643,7 +7643,7 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.364242052659392e-12</v>
+        <v>5.684341886080801e-14</v>
       </c>
       <c r="AF39" t="n">
         <v>0</v>
@@ -7661,7 +7661,7 @@
         <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>-1.364242052659392e-12</v>
+        <v>-5.684341886080801e-14</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -7693,19 +7693,19 @@
         <v>6</v>
       </c>
       <c r="E40" t="n">
-        <v>1.25478331428989e-12</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>3.136958285724726e-10</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>-5.600381307339044e-16</v>
+        <v>-6.63157692652396e-17</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.004999999999999622</v>
+        <v>-0.005000000000000043</v>
       </c>
       <c r="I40" t="n">
-        <v>0.008660254037843944</v>
+        <v>0.008660254037844498</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -7717,13 +7717,13 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.02999999999999752</v>
+        <v>0.03000000000000024</v>
       </c>
       <c r="N40" t="n">
-        <v>0.007499999999999598</v>
+        <v>0.007500000000000032</v>
       </c>
       <c r="O40" t="n">
-        <v>-0.004330127018921832</v>
+        <v>-0.004330127018922303</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
@@ -7735,13 +7735,13 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>-0.007499999999999245</v>
+        <v>-0.007500000000000047</v>
       </c>
       <c r="T40" t="n">
-        <v>0.0009449111825227839</v>
+        <v>0.0009449111825230567</v>
       </c>
       <c r="U40" t="n">
-        <v>-0.006546536707079803</v>
+        <v>-0.006546536707079898</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -7753,13 +7753,13 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>-0.007499999999999218</v>
+        <v>-0.007500000000000047</v>
       </c>
       <c r="Z40" t="n">
-        <v>0.01984313483298294</v>
+        <v>0.01984313483298453</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.02291287847477731</v>
+        <v>0.02291287847477944</v>
       </c>
       <c r="AB40" t="n">
         <v>0</v>
@@ -7771,7 +7771,7 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>-1.250555214937776e-12</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
         <v>0</v>
@@ -7789,7 +7789,7 @@
         <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.250555214937776e-12</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -7821,19 +7821,19 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.448144922727576e-12</v>
+        <v>7.24072461363788e-13</v>
       </c>
       <c r="F41" t="n">
-        <v>-3.62036230681894e-10</v>
+        <v>1.81018115340947e-10</v>
       </c>
       <c r="G41" t="n">
-        <v>0.01999999999999778</v>
+        <v>0.02000000000000019</v>
       </c>
       <c r="H41" t="n">
-        <v>0.009999999999999551</v>
+        <v>0.01000000000000005</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.005773502691895869</v>
+        <v>-0.005773502691896375</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -7845,10 +7845,10 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.05999999999999572</v>
+        <v>0.0600000000000005</v>
       </c>
       <c r="N41" t="n">
-        <v>-0.009999999999999452</v>
+        <v>-0.01000000000000008</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -7863,13 +7863,13 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0.01788854381999692</v>
+        <v>0.01788854381999845</v>
       </c>
       <c r="T41" t="n">
-        <v>-0.01341640786499696</v>
+        <v>-0.01341640786499889</v>
       </c>
       <c r="U41" t="n">
-        <v>-0.005773502691895869</v>
+        <v>-0.005773502691896375</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -7881,10 +7881,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.01788854381999689</v>
+        <v>0.01788854381999847</v>
       </c>
       <c r="Z41" t="n">
-        <v>-0.05813776741499045</v>
+        <v>-0.05813776741499502</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -7899,7 +7899,7 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.477928890381008e-12</v>
+        <v>-7.958078640513122e-13</v>
       </c>
       <c r="AF41" t="n">
         <v>0</v>
@@ -7917,7 +7917,7 @@
         <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>-1.477928890381008e-12</v>
+        <v>7.958078640513122e-13</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7949,19 +7949,19 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E42" t="n">
-        <v>1.592959415000334e-12</v>
+        <v>-5.792579690910304e-13</v>
       </c>
       <c r="F42" t="n">
-        <v>3.982398537500833e-10</v>
+        <v>-1.448144922727576e-10</v>
       </c>
       <c r="G42" t="n">
-        <v>0.01999999999999778</v>
+        <v>0.02000000000000019</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.009999999999999554</v>
+        <v>-0.01000000000000005</v>
       </c>
       <c r="I42" t="n">
-        <v>0.005773502691895859</v>
+        <v>0.005773502691896366</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -7973,10 +7973,10 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.05999999999999572</v>
+        <v>0.0600000000000005</v>
       </c>
       <c r="N42" t="n">
-        <v>0.009999999999999454</v>
+        <v>0.01000000000000008</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -7991,13 +7991,13 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>-0.01788854381999693</v>
+        <v>-0.01788854381999845</v>
       </c>
       <c r="T42" t="n">
-        <v>0.01341640786499695</v>
+        <v>0.01341640786499889</v>
       </c>
       <c r="U42" t="n">
-        <v>-0.005773502691895859</v>
+        <v>-0.005773502691896366</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -8009,10 +8009,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>-0.01788854381999689</v>
+        <v>-0.01788854381999846</v>
       </c>
       <c r="Z42" t="n">
-        <v>0.05813776741499045</v>
+        <v>0.05813776741499501</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -8027,7 +8027,7 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>-1.591615728102624e-12</v>
+        <v>5.684341886080801e-13</v>
       </c>
       <c r="AF42" t="n">
         <v>0</v>
@@ -8045,7 +8045,7 @@
         <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.591615728102624e-12</v>
+        <v>-5.684341886080801e-13</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -8077,19 +8077,19 @@
         <v>6</v>
       </c>
       <c r="E43" t="n">
-        <v>-1.61907524424502e-12</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>-4.04768811061255e-10</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.02999999999999752</v>
+        <v>0.03000000000000024</v>
       </c>
       <c r="H43" t="n">
-        <v>0.007499999999999598</v>
+        <v>0.007500000000000032</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.004330127018921832</v>
+        <v>-0.004330127018922303</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -8101,10 +8101,10 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.05999999999999572</v>
+        <v>0.0600000000000005</v>
       </c>
       <c r="N43" t="n">
-        <v>-0.009999999999999452</v>
+        <v>-0.01000000000000008</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -8119,13 +8119,13 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.02249999999999831</v>
+        <v>0.02250000000000019</v>
       </c>
       <c r="T43" t="n">
-        <v>-0.0141736677378447</v>
+        <v>-0.01417366773784619</v>
       </c>
       <c r="U43" t="n">
-        <v>0.01636634176769808</v>
+        <v>0.0163663417676995</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -8137,13 +8137,13 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.02249999999999827</v>
+        <v>0.02250000000000019</v>
       </c>
       <c r="Z43" t="n">
-        <v>-0.04063118084848914</v>
+        <v>-0.04063118084849227</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.03927922024247583</v>
+        <v>0.03927922024247896</v>
       </c>
       <c r="AB43" t="n">
         <v>0</v>
@@ -8155,7 +8155,7 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.818989403545856e-12</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
         <v>0</v>
@@ -8173,7 +8173,7 @@
         <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>-1.818989403545856e-12</v>
+        <v>0</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -8205,19 +8205,19 @@
         <v>6</v>
       </c>
       <c r="E44" t="n">
-        <v>1.295260195396016e-12</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>3.23815048849004e-10</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0.02999999999999752</v>
+        <v>0.03000000000000023</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.007499999999999597</v>
+        <v>-0.007500000000000036</v>
       </c>
       <c r="I44" t="n">
-        <v>0.004330127018921823</v>
+        <v>0.004330127018922292</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -8229,10 +8229,10 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.05999999999999572</v>
+        <v>0.0600000000000005</v>
       </c>
       <c r="N44" t="n">
-        <v>0.009999999999999454</v>
+        <v>0.01000000000000008</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -8247,13 +8247,13 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>-0.0224999999999983</v>
+        <v>-0.02250000000000019</v>
       </c>
       <c r="T44" t="n">
-        <v>0.0141736677378447</v>
+        <v>0.01417366773784618</v>
       </c>
       <c r="U44" t="n">
-        <v>0.01636634176769809</v>
+        <v>0.01636634176769951</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -8265,13 +8265,13 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>-0.02249999999999827</v>
+        <v>-0.02250000000000019</v>
       </c>
       <c r="Z44" t="n">
-        <v>0.04063118084848914</v>
+        <v>0.04063118084849227</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.03927922024247583</v>
+        <v>0.03927922024247896</v>
       </c>
       <c r="AB44" t="n">
         <v>0</v>
@@ -8283,7 +8283,7 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>-1.13686837721616e-12</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
         <v>0</v>
@@ -8301,7 +8301,7 @@
         <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.13686837721616e-12</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>

--- a/outputs/validation_truss_fab_error.xlsx
+++ b/outputs/validation_truss_fab_error.xlsx
@@ -538,7 +538,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-4.340689376152277e-19</v>
+        <v>-1.676274217120448e-17</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -556,7 +556,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>4.340689376152277e-19</v>
+        <v>1.676274217120448e-17</v>
       </c>
     </row>
     <row r="4">
@@ -573,13 +573,13 @@
         <v>2.598076211353316</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.609820512624577e-17</v>
+        <v>-1.93310952988333e-16</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002500000000000045</v>
+        <v>0.002499999999999709</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.004330127018922291</v>
+        <v>-0.004330127018921833</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -591,7 +591,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.005000000000000108</v>
+        <v>0.004999999999999542</v>
       </c>
     </row>
     <row r="5">
@@ -608,13 +608,13 @@
         <v>2.598076211353316</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.58091034875743e-17</v>
+        <v>-1.925891125394515e-16</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.002500000000000048</v>
+        <v>-0.002499999999999708</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004330127018922295</v>
+        <v>0.004330127018921839</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -626,7 +626,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.005000000000000112</v>
+        <v>0.004999999999999546</v>
       </c>
     </row>
     <row r="6">
@@ -643,13 +643,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>4.217979690080612e-17</v>
+        <v>-6.656716817340045e-16</v>
       </c>
       <c r="F6" t="n">
-        <v>2.496555289566721e-17</v>
+        <v>-2.662702988502231e-16</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.005773502691896366</v>
+        <v>-0.005773502691895882</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005773502691896366</v>
+        <v>0.005773502691895882</v>
       </c>
     </row>
     <row r="7">
@@ -678,13 +678,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>4.237319201299675e-17</v>
+        <v>-6.6479308875418e-16</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.715856455137496e-17</v>
+        <v>2.654651198196905e-16</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00577350269189637</v>
+        <v>0.005773502691895886</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -696,7 +696,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00577350269189637</v>
+        <v>0.005773502691895886</v>
       </c>
     </row>
     <row r="8">
@@ -713,13 +713,13 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E8" t="n">
-        <v>-6.640573517909717e-17</v>
+        <v>-5.60108479708646e-16</v>
       </c>
       <c r="F8" t="n">
-        <v>0.005000000000000042</v>
+        <v>0.004999999999999626</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.008660254037844501</v>
+        <v>-0.008660254037843948</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -731,7 +731,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01000000000000012</v>
+        <v>0.009999999999999433</v>
       </c>
     </row>
     <row r="9">
@@ -748,13 +748,13 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E9" t="n">
-        <v>-6.63157692652396e-17</v>
+        <v>-5.600381307339044e-16</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.005000000000000043</v>
+        <v>-0.004999999999999622</v>
       </c>
       <c r="G9" t="n">
-        <v>0.008660254037844498</v>
+        <v>0.008660254037843944</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -766,7 +766,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01000000000000012</v>
+        <v>0.009999999999999428</v>
       </c>
     </row>
     <row r="10">
@@ -783,13 +783,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02000000000000019</v>
+        <v>0.01999999999999778</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01000000000000005</v>
+        <v>0.009999999999999551</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.005773502691896375</v>
+        <v>-0.005773502691895869</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -801,7 +801,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.02309401076758525</v>
+        <v>0.02309401076758282</v>
       </c>
     </row>
     <row r="11">
@@ -818,13 +818,13 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02000000000000019</v>
+        <v>0.01999999999999778</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.01000000000000005</v>
+        <v>-0.009999999999999554</v>
       </c>
       <c r="G11" t="n">
-        <v>0.005773502691896366</v>
+        <v>0.005773502691895859</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -836,7 +836,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.02309401076758524</v>
+        <v>0.02309401076758282</v>
       </c>
     </row>
     <row r="12">
@@ -853,13 +853,13 @@
         <v>2.598076211353316</v>
       </c>
       <c r="E12" t="n">
-        <v>0.03000000000000024</v>
+        <v>0.02999999999999752</v>
       </c>
       <c r="F12" t="n">
-        <v>0.007500000000000032</v>
+        <v>0.007499999999999598</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.004330127018922303</v>
+        <v>-0.004330127018921832</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -871,7 +871,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.03122498999199224</v>
+        <v>0.03122498999198946</v>
       </c>
     </row>
     <row r="13">
@@ -888,13 +888,13 @@
         <v>2.598076211353316</v>
       </c>
       <c r="E13" t="n">
-        <v>0.03000000000000023</v>
+        <v>0.02999999999999752</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.007500000000000036</v>
+        <v>-0.007499999999999597</v>
       </c>
       <c r="G13" t="n">
-        <v>0.004330127018922292</v>
+        <v>0.004330127018921823</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -906,7 +906,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.03122498999199224</v>
+        <v>0.03122498999198946</v>
       </c>
     </row>
     <row r="14">
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0600000000000005</v>
+        <v>0.05999999999999572</v>
       </c>
       <c r="F14" t="n">
-        <v>0.01000000000000008</v>
+        <v>0.009999999999999454</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -941,7 +941,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0608276253029827</v>
+        <v>0.06082762530297788</v>
       </c>
     </row>
     <row r="15">
@@ -958,10 +958,10 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0600000000000005</v>
+        <v>0.05999999999999572</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.01000000000000008</v>
+        <v>-0.009999999999999452</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -976,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0608276253029827</v>
+        <v>0.06082762530297788</v>
       </c>
     </row>
   </sheetData>
@@ -1032,16 +1032,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0608276253029827</v>
+        <v>0.06082762530297788</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0600000000000005</v>
+        <v>0.05999999999999572</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.01000000000000008</v>
+        <v>0.009999999999999454</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -1054,16 +1054,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0600000000000005</v>
+        <v>0.05999999999999572</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0600000000000005</v>
+        <v>0.05999999999999572</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.01000000000000008</v>
+        <v>0.009999999999999454</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.01000000000000008</v>
+        <v>-0.009999999999999554</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0600000000000005</v>
+        <v>0.01999999999999778</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.01000000000000008</v>
+        <v>-0.009999999999999554</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.005773502691895859</v>
       </c>
     </row>
     <row r="5">
@@ -1101,16 +1101,16 @@
         <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.008660254037844501</v>
+        <v>-0.008660254037843948</v>
       </c>
       <c r="D5" t="n">
-        <v>-6.640573517909717e-17</v>
+        <v>-5.60108479708646e-16</v>
       </c>
       <c r="E5" t="n">
-        <v>0.005000000000000042</v>
+        <v>0.004999999999999626</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.008660254037844501</v>
+        <v>-0.008660254037843948</v>
       </c>
     </row>
   </sheetData>
@@ -1154,13 +1154,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1.4210854715202e-13</v>
+        <v>3.389288849575678e-12</v>
       </c>
       <c r="C2" t="n">
-        <v>-5.115907697472721e-13</v>
+        <v>1.91278104466619e-11</v>
       </c>
       <c r="D2" t="n">
-        <v>2.629008122312371e-13</v>
+        <v>2.586375558166765e-12</v>
       </c>
     </row>
     <row r="3">
@@ -1169,10 +1169,10 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>7.389644451905042e-13</v>
+        <v>-1.875832822406664e-11</v>
       </c>
       <c r="D3" t="n">
-        <v>-2.273736754432321e-13</v>
+        <v>-2.557953848736361e-12</v>
       </c>
     </row>
     <row r="4">
@@ -1182,7 +1182,7 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>3.410605131648481e-13</v>
+        <v>-2.046363078989089e-12</v>
       </c>
     </row>
     <row r="5">
@@ -1192,7 +1192,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>-2.273736754432321e-13</v>
+        <v>2.273736754432321e-12</v>
       </c>
     </row>
   </sheetData>
@@ -1275,16 +1275,16 @@
         <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>2.496555289566721e-17</v>
+        <v>-2.662702988502231e-16</v>
       </c>
       <c r="G2" t="n">
-        <v>4.160925482611201e-18</v>
+        <v>-4.437838314170385e-17</v>
       </c>
       <c r="H2" t="n">
-        <v>1.165059135131136e-12</v>
+        <v>-1.242594727967708e-11</v>
       </c>
       <c r="I2" t="n">
-        <v>2.912647837827841e-10</v>
+        <v>-3.10648681991927e-09</v>
       </c>
     </row>
     <row r="3">
@@ -1306,16 +1306,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F3" t="n">
-        <v>-9.974659986866641e-18</v>
+        <v>-7.24247051220317e-17</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.919624209497481e-18</v>
+        <v>-1.393814099939475e-17</v>
       </c>
       <c r="H3" t="n">
-        <v>-5.374947786592948e-13</v>
+        <v>-3.902679479830532e-12</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.343736946648237e-10</v>
+        <v>-9.756698699576329e-10</v>
       </c>
     </row>
     <row r="4">
@@ -1337,16 +1337,16 @@
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.734723475976807e-18</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-5.782411586589357e-19</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.61907524424502e-13</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-4.04768811061255e-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1368,16 +1368,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.170938346284345e-17</v>
+        <v>-3.165870343657673e-17</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.253471898105739e-18</v>
+        <v>-6.092720317100702e-18</v>
       </c>
       <c r="H5" t="n">
-        <v>-6.309721314696069e-13</v>
+        <v>-1.705961688788196e-12</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.577430328674017e-10</v>
+        <v>-4.264904221970491e-10</v>
       </c>
     </row>
     <row r="6">
@@ -1399,16 +1399,16 @@
         <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>2.602085213965211e-18</v>
+        <v>8.673617379884035e-19</v>
       </c>
       <c r="G6" t="n">
-        <v>4.336808689942018e-19</v>
+        <v>1.445602896647339e-19</v>
       </c>
       <c r="H6" t="n">
-        <v>1.214306433183765e-13</v>
+        <v>4.04768811061255e-14</v>
       </c>
       <c r="I6" t="n">
-        <v>3.035766082959412e-11</v>
+        <v>1.011922027653137e-11</v>
       </c>
     </row>
     <row r="7">
@@ -1430,16 +1430,16 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01000000000000003</v>
+        <v>0.009999999999999816</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001666666666666671</v>
+        <v>0.001666666666666636</v>
       </c>
       <c r="H7" t="n">
-        <v>466.6666666666679</v>
+        <v>466.666666666658</v>
       </c>
       <c r="I7" t="n">
-        <v>116666.666666667</v>
+        <v>116666.6666666645</v>
       </c>
     </row>
     <row r="8">
@@ -1461,16 +1461,16 @@
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>8.673617379884035e-18</v>
+        <v>6.938893903907228e-18</v>
       </c>
       <c r="G8" t="n">
-        <v>1.445602896647339e-18</v>
+        <v>1.156482317317871e-18</v>
       </c>
       <c r="H8" t="n">
-        <v>4.04768811061255e-13</v>
+        <v>3.23815048849004e-13</v>
       </c>
       <c r="I8" t="n">
-        <v>1.011922027653137e-10</v>
+        <v>8.095376221225099e-11</v>
       </c>
     </row>
     <row r="9">
@@ -1492,16 +1492,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.214306433183765e-17</v>
+        <v>1.387778780781446e-17</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.336933820257803e-18</v>
+        <v>2.670781508866061e-18</v>
       </c>
       <c r="H9" t="n">
-        <v>-6.54341469672185e-13</v>
+        <v>7.478188224824971e-13</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.635853674180462e-10</v>
+        <v>1.869547056206243e-10</v>
       </c>
     </row>
     <row r="10">
@@ -1523,16 +1523,16 @@
         <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.602085213965211e-18</v>
+        <v>4.336808689942018e-19</v>
       </c>
       <c r="G10" t="n">
-        <v>-8.673617379884035e-19</v>
+        <v>1.445602896647339e-19</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.42861286636753e-13</v>
+        <v>4.04768811061255e-14</v>
       </c>
       <c r="I10" t="n">
-        <v>-6.071532165918825e-11</v>
+        <v>1.011922027653137e-11</v>
       </c>
     </row>
     <row r="11">
@@ -1554,16 +1554,16 @@
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>-9.71445146547012e-17</v>
       </c>
       <c r="G11" t="n">
-        <v>4.625929269271485e-18</v>
+        <v>-1.61907524424502e-17</v>
       </c>
       <c r="H11" t="n">
-        <v>1.295260195396016e-12</v>
+        <v>-4.533410683886055e-12</v>
       </c>
       <c r="I11" t="n">
-        <v>3.23815048849004e-10</v>
+        <v>-1.133352670971514e-09</v>
       </c>
     </row>
     <row r="12">
@@ -1585,16 +1585,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.214306433183765e-17</v>
+        <v>5.551115123125783e-17</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.336933820257803e-18</v>
+        <v>1.068312603546424e-17</v>
       </c>
       <c r="H12" t="n">
-        <v>-6.54341469672185e-13</v>
+        <v>2.991275289929988e-12</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.635853674180462e-10</v>
+        <v>7.47818822482497e-10</v>
       </c>
     </row>
     <row r="13">
@@ -1616,16 +1616,16 @@
         <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.715856455137496e-17</v>
+        <v>2.654651198196905e-16</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.526427425229161e-18</v>
+        <v>4.424418663661508e-17</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.267399679064165e-12</v>
+        <v>1.238837225825222e-11</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.168499197660412e-10</v>
+        <v>3.097093064563055e-09</v>
       </c>
     </row>
     <row r="14">
@@ -1647,16 +1647,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F14" t="n">
-        <v>9.107298248878237e-18</v>
+        <v>7.589415207398531e-17</v>
       </c>
       <c r="G14" t="n">
-        <v>1.752700365193353e-18</v>
+        <v>1.460583637661127e-17</v>
       </c>
       <c r="H14" t="n">
-        <v>4.907561022541388e-13</v>
+        <v>4.089634185451156e-12</v>
       </c>
       <c r="I14" t="n">
-        <v>1.226890255635347e-10</v>
+        <v>1.022408546362789e-09</v>
       </c>
     </row>
     <row r="15">
@@ -1678,16 +1678,16 @@
         <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>8.673617379884035e-19</v>
+        <v>1.734723475976807e-18</v>
       </c>
       <c r="G15" t="n">
-        <v>2.891205793294678e-19</v>
+        <v>5.782411586589357e-19</v>
       </c>
       <c r="H15" t="n">
-        <v>8.095376221225099e-14</v>
+        <v>1.61907524424502e-13</v>
       </c>
       <c r="I15" t="n">
-        <v>2.023844055306275e-11</v>
+        <v>4.04768811061255e-11</v>
       </c>
     </row>
     <row r="16">
@@ -1709,16 +1709,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F16" t="n">
-        <v>9.974659986866641e-18</v>
+        <v>3.079134169858833e-17</v>
       </c>
       <c r="G16" t="n">
-        <v>1.919624209497481e-18</v>
+        <v>5.925796472796573e-18</v>
       </c>
       <c r="H16" t="n">
-        <v>5.374947786592948e-13</v>
+        <v>1.65922301238304e-12</v>
       </c>
       <c r="I16" t="n">
-        <v>1.343736946648237e-10</v>
+        <v>4.148057530957601e-10</v>
       </c>
     </row>
     <row r="17">
@@ -1740,16 +1740,16 @@
         <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>-7.806255641895632e-18</v>
+        <v>-4.336808689942018e-18</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.301042606982605e-18</v>
+        <v>-7.228014483236697e-19</v>
       </c>
       <c r="H17" t="n">
-        <v>-3.642919299551295e-13</v>
+        <v>-2.023844055306275e-13</v>
       </c>
       <c r="I17" t="n">
-        <v>-9.107298248878237e-11</v>
+        <v>-5.059610138265687e-11</v>
       </c>
     </row>
     <row r="18">
@@ -1771,16 +1771,16 @@
         <v>6</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.01000000000000003</v>
+        <v>-0.00999999999999982</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.001666666666666671</v>
+        <v>-0.001666666666666637</v>
       </c>
       <c r="H18" t="n">
-        <v>-466.6666666666679</v>
+        <v>-466.6666666666582</v>
       </c>
       <c r="I18" t="n">
-        <v>-116666.666666667</v>
+        <v>-116666.6666666645</v>
       </c>
     </row>
     <row r="19">
@@ -1802,16 +1802,16 @@
         <v>6</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.734723475976807e-18</v>
+        <v>-5.204170427930421e-18</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.891205793294678e-19</v>
+        <v>-8.673617379884035e-19</v>
       </c>
       <c r="H19" t="n">
-        <v>-8.095376221225099e-14</v>
+        <v>-2.42861286636753e-13</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.023844055306275e-11</v>
+        <v>-6.071532165918825e-11</v>
       </c>
     </row>
     <row r="20">
@@ -1833,16 +1833,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F20" t="n">
-        <v>1.214306433183765e-17</v>
+        <v>-1.387778780781446e-17</v>
       </c>
       <c r="G20" t="n">
-        <v>2.336933820257803e-18</v>
+        <v>-2.670781508866061e-18</v>
       </c>
       <c r="H20" t="n">
-        <v>6.54341469672185e-13</v>
+        <v>-7.478188224824971e-13</v>
       </c>
       <c r="I20" t="n">
-        <v>1.635853674180462e-10</v>
+        <v>-1.869547056206243e-10</v>
       </c>
     </row>
     <row r="21">
@@ -1864,16 +1864,16 @@
         <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>8.673617379884035e-19</v>
+        <v>3.035766082959412e-18</v>
       </c>
       <c r="G21" t="n">
-        <v>2.891205793294678e-19</v>
+        <v>1.011922027653138e-18</v>
       </c>
       <c r="H21" t="n">
-        <v>8.095376221225099e-14</v>
+        <v>2.833381677428785e-13</v>
       </c>
       <c r="I21" t="n">
-        <v>2.023844055306275e-11</v>
+        <v>7.083454193571961e-11</v>
       </c>
     </row>
     <row r="22">
@@ -1895,16 +1895,16 @@
         <v>6</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.949029909160572e-17</v>
+        <v>1.023486850826316e-16</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.915049848600954e-18</v>
+        <v>1.70581141804386e-17</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.376213957608267e-12</v>
+        <v>4.776271970522808e-12</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.440534894020667e-10</v>
+        <v>1.194067992630702e-09</v>
       </c>
     </row>
     <row r="23">
@@ -1926,16 +1926,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F23" t="n">
-        <v>8.673617379884035e-18</v>
+        <v>-5.898059818321144e-17</v>
       </c>
       <c r="G23" t="n">
-        <v>1.669238443041288e-18</v>
+        <v>-1.135082141268076e-17</v>
       </c>
       <c r="H23" t="n">
-        <v>4.673867640515606e-13</v>
+        <v>-3.178229995550613e-12</v>
       </c>
       <c r="I23" t="n">
-        <v>1.168466910128902e-10</v>
+        <v>-7.945574988876531e-10</v>
       </c>
     </row>
     <row r="24">
@@ -1957,16 +1957,16 @@
         <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.340689376152277e-19</v>
+        <v>-1.676274217120448e-17</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.446896458717426e-19</v>
+        <v>-5.587580723734825e-18</v>
       </c>
       <c r="H24" t="n">
-        <v>-4.051310084408792e-14</v>
+        <v>-1.564522602645751e-12</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.012827521102198e-11</v>
+        <v>-3.911306506614377e-10</v>
       </c>
     </row>
     <row r="25">
@@ -1988,16 +1988,16 @@
         <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>2.891016386714714e-19</v>
+        <v>7.218404488814572e-19</v>
       </c>
       <c r="G25" t="n">
-        <v>9.636721289049048e-20</v>
+        <v>2.406134829604857e-19</v>
       </c>
       <c r="H25" t="n">
-        <v>2.698281960933733e-14</v>
+        <v>6.7371775228936e-14</v>
       </c>
       <c r="I25" t="n">
-        <v>6.745704902334333e-12</v>
+        <v>1.6842943807234e-11</v>
       </c>
     </row>
     <row r="26">
@@ -2019,16 +2019,16 @@
         <v>3</v>
       </c>
       <c r="F26" t="n">
-        <v>1.933951121906287e-19</v>
+        <v>8.785929798245307e-19</v>
       </c>
       <c r="G26" t="n">
-        <v>6.446503739687624e-20</v>
+        <v>2.928643266081769e-19</v>
       </c>
       <c r="H26" t="n">
-        <v>1.805021047112535e-14</v>
+        <v>8.200201145028953e-14</v>
       </c>
       <c r="I26" t="n">
-        <v>4.512552617781336e-12</v>
+        <v>2.050050286257238e-11</v>
       </c>
     </row>
     <row r="27">
@@ -2050,16 +2050,16 @@
         <v>3</v>
       </c>
       <c r="F27" t="n">
-        <v>8.996591385756622e-20</v>
+        <v>7.034897474159622e-20</v>
       </c>
       <c r="G27" t="n">
-        <v>2.998863795252207e-20</v>
+        <v>2.344965824719874e-20</v>
       </c>
       <c r="H27" t="n">
-        <v>8.39681862670618e-15</v>
+        <v>6.565904309215647e-15</v>
       </c>
       <c r="I27" t="n">
-        <v>2.099204656676545e-12</v>
+        <v>1.641476077303912e-12</v>
       </c>
     </row>
     <row r="28">
@@ -2143,16 +2143,16 @@
         <v>3</v>
       </c>
       <c r="F30" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>2.312964634635743e-18</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>6.476300976980079e-13</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>1.61907524424502e-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2174,16 +2174,16 @@
         <v>6</v>
       </c>
       <c r="F31" t="n">
-        <v>2.168404344971009e-19</v>
+        <v>-3.057450126409123e-17</v>
       </c>
       <c r="G31" t="n">
-        <v>3.614007241618348e-20</v>
+        <v>-5.095750210681871e-18</v>
       </c>
       <c r="H31" t="n">
-        <v>1.011922027653137e-14</v>
+        <v>-1.426810058990924e-12</v>
       </c>
       <c r="I31" t="n">
-        <v>2.529805069132844e-12</v>
+        <v>-3.56702514747731e-10</v>
       </c>
     </row>
     <row r="32">
@@ -2205,16 +2205,16 @@
         <v>6</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.084396206796017e-18</v>
+        <v>2.54457366959455e-17</v>
       </c>
       <c r="G32" t="n">
-        <v>-1.807327011326696e-19</v>
+        <v>4.240956115990917e-18</v>
       </c>
       <c r="H32" t="n">
-        <v>-5.060515631714747e-14</v>
+        <v>1.187467712477457e-12</v>
       </c>
       <c r="I32" t="n">
-        <v>-1.265128907928687e-11</v>
+        <v>2.968669281193641e-10</v>
       </c>
     </row>
     <row r="33">
@@ -2236,16 +2236,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F33" t="n">
-        <v>-5.341491050333823e-18</v>
+        <v>-5.986528605649763e-17</v>
       </c>
       <c r="G33" t="n">
-        <v>-7.962624726502119e-19</v>
+        <v>-8.924189940986602e-18</v>
       </c>
       <c r="H33" t="n">
-        <v>-2.229534923420594e-13</v>
+        <v>-2.498773183476249e-12</v>
       </c>
       <c r="I33" t="n">
-        <v>-5.573837308551484e-11</v>
+        <v>-6.246932958690621e-10</v>
       </c>
     </row>
     <row r="34">
@@ -2267,16 +2267,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F34" t="n">
-        <v>3.272369188478197e-18</v>
+        <v>5.204150456663151e-17</v>
       </c>
       <c r="G34" t="n">
-        <v>4.878159968608712e-19</v>
+        <v>7.757889457490252e-18</v>
       </c>
       <c r="H34" t="n">
-        <v>1.36588479121044e-13</v>
+        <v>2.172209048097271e-12</v>
       </c>
       <c r="I34" t="n">
-        <v>3.414711978026099e-11</v>
+        <v>5.430522620243177e-10</v>
       </c>
     </row>
     <row r="35">
@@ -2298,16 +2298,16 @@
         <v>6</v>
       </c>
       <c r="F35" t="n">
-        <v>4.336808689942018e-19</v>
+        <v>-2.818925648462312e-17</v>
       </c>
       <c r="G35" t="n">
-        <v>7.228014483236696e-20</v>
+        <v>-4.698209414103853e-18</v>
       </c>
       <c r="H35" t="n">
-        <v>2.023844055306275e-14</v>
+        <v>-1.315498635949079e-12</v>
       </c>
       <c r="I35" t="n">
-        <v>5.059610138265687e-12</v>
+        <v>-3.288746589872696e-10</v>
       </c>
     </row>
     <row r="36">
@@ -2329,16 +2329,16 @@
         <v>6</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.084202172485504e-18</v>
+        <v>2.753873518113181e-17</v>
       </c>
       <c r="G36" t="n">
-        <v>-1.807003620809174e-19</v>
+        <v>4.589789196855302e-18</v>
       </c>
       <c r="H36" t="n">
-        <v>-5.059610138265687e-14</v>
+        <v>1.285140975119484e-12</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.264902534566422e-11</v>
+        <v>3.212852437798711e-10</v>
       </c>
     </row>
     <row r="37">
@@ -2360,16 +2360,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F37" t="n">
-        <v>-3.029331506209172e-18</v>
+        <v>-5.741860712598695e-17</v>
       </c>
       <c r="G37" t="n">
-        <v>-4.51586078284369e-19</v>
+        <v>-8.55946058047071e-18</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.264441019196233e-13</v>
+        <v>-2.396648962531799e-12</v>
       </c>
       <c r="I37" t="n">
-        <v>-3.161102547990584e-11</v>
+        <v>-5.991622406329497e-10</v>
       </c>
     </row>
     <row r="38">
@@ -2391,16 +2391,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F38" t="n">
-        <v>3.342586208752015e-18</v>
+        <v>5.506225291805303e-17</v>
       </c>
       <c r="G38" t="n">
-        <v>4.982833322281873e-19</v>
+        <v>8.208196034603516e-18</v>
       </c>
       <c r="H38" t="n">
-        <v>1.395193330238924e-13</v>
+        <v>2.298294889688984e-12</v>
       </c>
       <c r="I38" t="n">
-        <v>3.48798332559731e-11</v>
+        <v>5.745737224222461e-10</v>
       </c>
     </row>
     <row r="39">
@@ -2422,16 +2422,16 @@
         <v>6</v>
       </c>
       <c r="F39" t="n">
-        <v>-8.673617379884035e-19</v>
+        <v>-2.949029909160572e-17</v>
       </c>
       <c r="G39" t="n">
-        <v>-1.445602896647339e-19</v>
+        <v>-4.915049848600954e-18</v>
       </c>
       <c r="H39" t="n">
-        <v>-4.04768811061255e-14</v>
+        <v>-1.376213957608267e-12</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.011922027653137e-11</v>
+        <v>-3.440534894020667e-10</v>
       </c>
     </row>
     <row r="40">
@@ -2453,16 +2453,16 @@
         <v>6</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>2.688821387764051e-17</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>4.481368979606752e-18</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>1.25478331428989e-12</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>3.136958285724726e-10</v>
       </c>
     </row>
     <row r="41">
@@ -2484,16 +2484,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F41" t="n">
-        <v>1.734723475976807e-17</v>
+        <v>-3.469446951953614e-17</v>
       </c>
       <c r="G41" t="n">
-        <v>2.585973076299243e-18</v>
+        <v>-5.171946152598485e-18</v>
       </c>
       <c r="H41" t="n">
-        <v>7.24072461363788e-13</v>
+        <v>-1.448144922727576e-12</v>
       </c>
       <c r="I41" t="n">
-        <v>1.81018115340947e-10</v>
+        <v>-3.62036230681894e-10</v>
       </c>
     </row>
     <row r="42">
@@ -2515,16 +2515,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F42" t="n">
-        <v>-1.387778780781446e-17</v>
+        <v>3.816391647148976e-17</v>
       </c>
       <c r="G42" t="n">
-        <v>-2.068778461039394e-18</v>
+        <v>5.689140767858334e-18</v>
       </c>
       <c r="H42" t="n">
-        <v>-5.792579690910304e-13</v>
+        <v>1.592959415000334e-12</v>
       </c>
       <c r="I42" t="n">
-        <v>-1.448144922727576e-10</v>
+        <v>3.982398537500833e-10</v>
       </c>
     </row>
     <row r="43">
@@ -2546,16 +2546,16 @@
         <v>6</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>-3.469446951953614e-17</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>-5.782411586589357e-18</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>-1.61907524424502e-12</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>-4.04768811061255e-10</v>
       </c>
     </row>
     <row r="44">
@@ -2577,16 +2577,16 @@
         <v>6</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>2.775557561562891e-17</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>4.625929269271485e-18</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>1.295260195396016e-12</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>3.23815048849004e-10</v>
       </c>
     </row>
   </sheetData>
@@ -2829,10 +2829,10 @@
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>1.165059135131136e-12</v>
+        <v>-1.242594727967708e-11</v>
       </c>
       <c r="F2" t="n">
-        <v>2.912647837827841e-10</v>
+        <v>-3.10648681991927e-09</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -2853,13 +2853,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>4.217979690080612e-17</v>
+        <v>-6.656716817340045e-16</v>
       </c>
       <c r="N2" t="n">
-        <v>2.496555289566721e-17</v>
+        <v>-2.662702988502231e-16</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.005773502691896366</v>
+        <v>-0.005773502691895882</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -2889,13 +2889,13 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.496555289566721e-17</v>
+        <v>-2.662702988502231e-16</v>
       </c>
       <c r="Z2" t="n">
-        <v>-4.217979690080612e-17</v>
+        <v>6.656716817340045e-16</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.005773502691896366</v>
+        <v>-0.005773502691895882</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -2907,7 +2907,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-1.165059135131137e-12</v>
+        <v>1.242594727967708e-11</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -2925,7 +2925,7 @@
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.165059135131137e-12</v>
+        <v>-1.242594727967708e-11</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -2957,10 +2957,10 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E3" t="n">
-        <v>-5.374947786592948e-13</v>
+        <v>-3.902679479830532e-12</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.343736946648237e-10</v>
+        <v>-9.756698699576329e-10</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -2981,13 +2981,13 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.609820512624577e-17</v>
+        <v>-1.93310952988333e-16</v>
       </c>
       <c r="N3" t="n">
-        <v>0.002500000000000045</v>
+        <v>0.002499999999999709</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.004330127018922291</v>
+        <v>-0.004330127018921833</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -3017,13 +3017,13 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-9.974659986866641e-18</v>
+        <v>-7.24247051220317e-17</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.005000000000000108</v>
+        <v>0.004999999999999542</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.609820512624577e-17</v>
+        <v>1.93310952988333e-16</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -3035,7 +3035,7 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>5.374947786592948e-13</v>
+        <v>3.902679479830532e-12</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -3053,7 +3053,7 @@
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>-5.374947786592948e-13</v>
+        <v>-3.902679479830532e-12</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -3085,19 +3085,19 @@
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.61907524424502e-13</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-4.04768811061255e-11</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.609820512624577e-17</v>
+        <v>-1.93310952988333e-16</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002500000000000045</v>
+        <v>0.002499999999999709</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.004330127018922291</v>
+        <v>-0.004330127018921833</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -3109,13 +3109,13 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>4.217979690080612e-17</v>
+        <v>-6.656716817340045e-16</v>
       </c>
       <c r="N4" t="n">
-        <v>2.496555289566721e-17</v>
+        <v>-2.662702988502231e-16</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.005773502691896366</v>
+        <v>-0.005773502691895882</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -3127,13 +3127,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.005000000000000108</v>
+        <v>0.004999999999999543</v>
       </c>
       <c r="T4" t="n">
-        <v>-9.974659986866641e-18</v>
+        <v>-7.24247051220317e-17</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.609820512624577e-17</v>
+        <v>-1.93310952988333e-16</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -3145,13 +3145,13 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.005000000000000106</v>
+        <v>0.004999999999999543</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.002886751345948161</v>
+        <v>-0.002886751345948172</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.217979690080612e-17</v>
+        <v>-6.656716817340045e-16</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -3163,7 +3163,7 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.70530256582424e-13</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -3181,7 +3181,7 @@
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>-1.70530256582424e-13</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -3213,19 +3213,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E5" t="n">
-        <v>-6.309721314696069e-13</v>
+        <v>-1.705961688788196e-12</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.577430328674017e-10</v>
+        <v>-4.264904221970491e-10</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.609820512624577e-17</v>
+        <v>-1.93310952988333e-16</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002500000000000045</v>
+        <v>0.002499999999999709</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.004330127018922291</v>
+        <v>-0.004330127018921833</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -3237,13 +3237,13 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-6.640573517909717e-17</v>
+        <v>-5.60108479708646e-16</v>
       </c>
       <c r="N5" t="n">
-        <v>0.005000000000000042</v>
+        <v>0.004999999999999626</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.008660254037844501</v>
+        <v>-0.008660254037843948</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-9.974659986866641e-18</v>
+        <v>-7.24247051220317e-17</v>
       </c>
       <c r="T5" t="n">
-        <v>0.005000000000000108</v>
+        <v>0.004999999999999542</v>
       </c>
       <c r="U5" t="n">
-        <v>1.609820512624577e-17</v>
+        <v>1.93310952988333e-16</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -3273,13 +3273,13 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-2.168404344971009e-17</v>
+        <v>-1.040834085586084e-16</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01000000000000012</v>
+        <v>0.009999999999999433</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.640573517909717e-17</v>
+        <v>5.60108479708646e-16</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -3291,7 +3291,7 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>6.30972131469607e-13</v>
+        <v>1.705961688788196e-12</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>-6.30972131469607e-13</v>
+        <v>-1.705961688788196e-12</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -3341,19 +3341,19 @@
         <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>1.214306433183765e-13</v>
+        <v>4.04768811061255e-14</v>
       </c>
       <c r="F6" t="n">
-        <v>3.035766082959412e-11</v>
+        <v>1.011922027653137e-11</v>
       </c>
       <c r="G6" t="n">
-        <v>4.217979690080612e-17</v>
+        <v>-6.656716817340045e-16</v>
       </c>
       <c r="H6" t="n">
-        <v>2.496555289566721e-17</v>
+        <v>-2.662702988502231e-16</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.005773502691896366</v>
+        <v>-0.005773502691895882</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -3365,13 +3365,13 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-6.640573517909717e-17</v>
+        <v>-5.60108479708646e-16</v>
       </c>
       <c r="N6" t="n">
-        <v>0.005000000000000042</v>
+        <v>0.004999999999999626</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.008660254037844501</v>
+        <v>-0.008660254037843948</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -3383,13 +3383,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.005000000000000082</v>
+        <v>-0.004999999999999808</v>
       </c>
       <c r="T6" t="n">
-        <v>0.002886751345948204</v>
+        <v>0.00288675134594771</v>
       </c>
       <c r="U6" t="n">
-        <v>-4.217979690080612e-17</v>
+        <v>6.656716817340045e-16</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -3401,13 +3401,13 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.005000000000000079</v>
+        <v>-0.004999999999999808</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.00866025403784448</v>
+        <v>0.008660254037843844</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.640573517909717e-17</v>
+        <v>5.60108479708646e-16</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -3419,7 +3419,7 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-1.13686837721616e-13</v>
+        <v>-2.842170943040401e-14</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3437,7 +3437,7 @@
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.13686837721616e-13</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -3469,19 +3469,19 @@
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>466.6666666666679</v>
+        <v>466.666666666658</v>
       </c>
       <c r="F7" t="n">
-        <v>116666.666666667</v>
+        <v>116666.6666666645</v>
       </c>
       <c r="G7" t="n">
-        <v>4.217979690080612e-17</v>
+        <v>-6.656716817340045e-16</v>
       </c>
       <c r="H7" t="n">
-        <v>2.496555289566721e-17</v>
+        <v>-2.662702988502231e-16</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.005773502691896366</v>
+        <v>-0.005773502691895882</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -3493,13 +3493,13 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02000000000000019</v>
+        <v>0.01999999999999778</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01000000000000005</v>
+        <v>0.009999999999999551</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.005773502691896375</v>
+        <v>-0.005773502691895869</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -3511,13 +3511,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.496555289566721e-17</v>
+        <v>-2.662702988502231e-16</v>
       </c>
       <c r="T7" t="n">
-        <v>-4.217979690080612e-17</v>
+        <v>6.656716817340045e-16</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.005773502691896366</v>
+        <v>-0.005773502691895882</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -3529,13 +3529,13 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01000000000000005</v>
+        <v>0.009999999999999551</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.02000000000000019</v>
+        <v>-0.01999999999999778</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.005773502691896375</v>
+        <v>-0.005773502691895869</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -3547,7 +3547,7 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-1.4210854715202e-12</v>
+        <v>8.412825991399586e-12</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.4210854715202e-12</v>
+        <v>-8.412825991399586e-12</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -3597,19 +3597,19 @@
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>4.04768811061255e-13</v>
+        <v>3.23815048849004e-13</v>
       </c>
       <c r="F8" t="n">
-        <v>1.011922027653137e-10</v>
+        <v>8.095376221225099e-11</v>
       </c>
       <c r="G8" t="n">
-        <v>-6.640573517909717e-17</v>
+        <v>-5.60108479708646e-16</v>
       </c>
       <c r="H8" t="n">
-        <v>0.005000000000000042</v>
+        <v>0.004999999999999626</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.008660254037844501</v>
+        <v>-0.008660254037843948</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -3621,13 +3621,13 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02000000000000019</v>
+        <v>0.01999999999999778</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01000000000000005</v>
+        <v>0.009999999999999551</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.005773502691896375</v>
+        <v>-0.005773502691895869</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -3639,13 +3639,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01000000000000012</v>
+        <v>0.009999999999999433</v>
       </c>
       <c r="T8" t="n">
-        <v>-2.081668171172169e-17</v>
+        <v>-1.040834085586084e-16</v>
       </c>
       <c r="U8" t="n">
-        <v>-6.640573517909717e-17</v>
+        <v>-5.60108479708646e-16</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -3657,13 +3657,13 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01000000000000013</v>
+        <v>0.00999999999999944</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.005773502691896244</v>
+        <v>0.005773502691896063</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.02000000000000019</v>
+        <v>0.01999999999999778</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-3.979039320256561e-13</v>
+        <v>-3.410605131648481e-13</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3693,7 +3693,7 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.979039320256561e-13</v>
+        <v>3.410605131648481e-13</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -3725,19 +3725,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E9" t="n">
-        <v>-6.54341469672185e-13</v>
+        <v>7.478188224824971e-13</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.635853674180462e-10</v>
+        <v>1.869547056206243e-10</v>
       </c>
       <c r="G9" t="n">
-        <v>-6.640573517909717e-17</v>
+        <v>-5.60108479708646e-16</v>
       </c>
       <c r="H9" t="n">
-        <v>0.005000000000000042</v>
+        <v>0.004999999999999626</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.008660254037844501</v>
+        <v>-0.008660254037843948</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -3749,13 +3749,13 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.03000000000000024</v>
+        <v>0.02999999999999752</v>
       </c>
       <c r="N9" t="n">
-        <v>0.007500000000000032</v>
+        <v>0.007499999999999598</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.004330127018922303</v>
+        <v>-0.004330127018921832</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -3767,13 +3767,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.00866025403784448</v>
+        <v>0.008660254037843844</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.005000000000000077</v>
+        <v>-0.004999999999999807</v>
       </c>
       <c r="U9" t="n">
-        <v>-6.640573517909717e-17</v>
+        <v>-5.60108479708646e-16</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.008660254037844468</v>
+        <v>0.008660254037843857</v>
       </c>
       <c r="Z9" t="n">
-        <v>-7.849623728795052e-17</v>
+        <v>1.118896642005041e-16</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03000000000000024</v>
+        <v>0.02999999999999752</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -3803,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>6.252776074688882e-13</v>
+        <v>-7.389644451905042e-13</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -3821,7 +3821,7 @@
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>-6.252776074688882e-13</v>
+        <v>7.389644451905042e-13</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -3853,19 +3853,19 @@
         <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.42861286636753e-13</v>
+        <v>4.04768811061255e-14</v>
       </c>
       <c r="F10" t="n">
-        <v>-6.071532165918825e-11</v>
+        <v>1.011922027653137e-11</v>
       </c>
       <c r="G10" t="n">
-        <v>0.02000000000000019</v>
+        <v>0.01999999999999778</v>
       </c>
       <c r="H10" t="n">
-        <v>0.01000000000000005</v>
+        <v>0.009999999999999551</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.005773502691896375</v>
+        <v>-0.005773502691895869</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -3877,13 +3877,13 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.03000000000000024</v>
+        <v>0.02999999999999752</v>
       </c>
       <c r="N10" t="n">
-        <v>0.007500000000000032</v>
+        <v>0.007499999999999598</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.004330127018922303</v>
+        <v>-0.004330127018921832</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-7.632783294297951e-17</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01154700538379262</v>
+        <v>0.01154700538379193</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.02000000000000019</v>
+        <v>-0.01999999999999778</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -3913,13 +3913,13 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>-7.892991815694472e-17</v>
+        <v>1.114559833315099e-16</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.00866025403784447</v>
+        <v>0.008660254037843859</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.03000000000000024</v>
+        <v>-0.02999999999999752</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -3931,7 +3931,7 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.42861286636753e-13</v>
+        <v>-4.047688110612496e-14</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -3949,7 +3949,7 @@
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>-2.42861286636753e-13</v>
+        <v>4.047688110612496e-14</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -3981,19 +3981,19 @@
         <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>1.295260195396016e-12</v>
+        <v>-4.533410683886055e-12</v>
       </c>
       <c r="F11" t="n">
-        <v>3.23815048849004e-10</v>
+        <v>-1.133352670971514e-09</v>
       </c>
       <c r="G11" t="n">
-        <v>0.02000000000000019</v>
+        <v>0.01999999999999778</v>
       </c>
       <c r="H11" t="n">
-        <v>0.01000000000000005</v>
+        <v>0.009999999999999551</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.005773502691896375</v>
+        <v>-0.005773502691895869</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -4005,10 +4005,10 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0600000000000005</v>
+        <v>0.05999999999999572</v>
       </c>
       <c r="N11" t="n">
-        <v>0.01000000000000008</v>
+        <v>0.009999999999999454</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -4023,13 +4023,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01000000000000005</v>
+        <v>0.009999999999999551</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.02000000000000019</v>
+        <v>-0.01999999999999778</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.005773502691896375</v>
+        <v>-0.005773502691895869</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -4041,10 +4041,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.01000000000000008</v>
+        <v>0.009999999999999454</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.0600000000000005</v>
+        <v>-0.05999999999999572</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -4059,7 +4059,7 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-1.250555214937776e-12</v>
+        <v>4.547473508864641e-12</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -4077,7 +4077,7 @@
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.250555214937776e-12</v>
+        <v>-4.547473508864641e-12</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -4109,19 +4109,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.54341469672185e-13</v>
+        <v>2.991275289929988e-12</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.635853674180462e-10</v>
+        <v>7.47818822482497e-10</v>
       </c>
       <c r="G12" t="n">
-        <v>0.03000000000000024</v>
+        <v>0.02999999999999752</v>
       </c>
       <c r="H12" t="n">
-        <v>0.007500000000000032</v>
+        <v>0.007499999999999598</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.004330127018922303</v>
+        <v>-0.004330127018921832</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -4133,10 +4133,10 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0600000000000005</v>
+        <v>0.05999999999999572</v>
       </c>
       <c r="N12" t="n">
-        <v>0.01000000000000008</v>
+        <v>0.009999999999999454</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -4151,13 +4151,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.008660254037844468</v>
+        <v>0.008660254037843857</v>
       </c>
       <c r="T12" t="n">
-        <v>-7.849623728795052e-17</v>
+        <v>1.118896642005041e-16</v>
       </c>
       <c r="U12" t="n">
-        <v>0.03000000000000024</v>
+        <v>0.02999999999999752</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -4169,13 +4169,13 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.008660254037844456</v>
+        <v>0.008660254037843913</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.00500000000000004</v>
+        <v>0.004999999999999727</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.0600000000000005</v>
+        <v>0.05999999999999572</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -4187,7 +4187,7 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>6.821210263296962e-13</v>
+        <v>-3.012701199622825e-12</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -4205,7 +4205,7 @@
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>-6.821210263296962e-13</v>
+        <v>3.012701199622825e-12</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -4237,13 +4237,13 @@
         <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.267399679064165e-12</v>
+        <v>1.238837225825222e-11</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.168499197660412e-10</v>
+        <v>3.097093064563055e-09</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.340689376152277e-19</v>
+        <v>-1.676274217120448e-17</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -4261,13 +4261,13 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.237319201299675e-17</v>
+        <v>-6.6479308875418e-16</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.715856455137496e-17</v>
+        <v>2.654651198196905e-16</v>
       </c>
       <c r="O13" t="n">
-        <v>0.00577350269189637</v>
+        <v>0.005773502691895886</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -4282,7 +4282,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>4.340689376152277e-19</v>
+        <v>1.676274217120448e-17</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -4297,13 +4297,13 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>-2.715856455137496e-17</v>
+        <v>2.654651198196905e-16</v>
       </c>
       <c r="Z13" t="n">
-        <v>-4.237319201299675e-17</v>
+        <v>6.6479308875418e-16</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.00577350269189637</v>
+        <v>0.005773502691895886</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.267399679064165e-12</v>
+        <v>-1.238837225825223e-11</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -4333,7 +4333,7 @@
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>-1.267399679064165e-12</v>
+        <v>1.238837225825223e-11</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -4365,13 +4365,13 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E14" t="n">
-        <v>4.907561022541388e-13</v>
+        <v>4.089634185451156e-12</v>
       </c>
       <c r="F14" t="n">
-        <v>1.226890255635347e-10</v>
+        <v>1.022408546362789e-09</v>
       </c>
       <c r="G14" t="n">
-        <v>-4.340689376152277e-19</v>
+        <v>-1.676274217120448e-17</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -4389,13 +4389,13 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.58091034875743e-17</v>
+        <v>-1.925891125394515e-16</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.002500000000000048</v>
+        <v>-0.002499999999999708</v>
       </c>
       <c r="O14" t="n">
-        <v>0.004330127018922295</v>
+        <v>0.004330127018921839</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -4413,7 +4413,7 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>4.340689376152277e-19</v>
+        <v>1.676274217120448e-17</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -4425,13 +4425,13 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>9.107298248878237e-18</v>
+        <v>7.589415207398531e-17</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0.005000000000000112</v>
+        <v>-0.004999999999999546</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.58091034875743e-17</v>
+        <v>1.925891125394515e-16</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -4443,7 +4443,7 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>-4.907561022541388e-13</v>
+        <v>-4.089634185451156e-12</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -4461,7 +4461,7 @@
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>4.907561022541388e-13</v>
+        <v>4.089634185451156e-12</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -4493,19 +4493,19 @@
         <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>8.095376221225099e-14</v>
+        <v>1.61907524424502e-13</v>
       </c>
       <c r="F15" t="n">
-        <v>2.023844055306275e-11</v>
+        <v>4.04768811061255e-11</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.58091034875743e-17</v>
+        <v>-1.925891125394515e-16</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.002500000000000048</v>
+        <v>-0.002499999999999708</v>
       </c>
       <c r="I15" t="n">
-        <v>0.004330127018922295</v>
+        <v>0.004330127018921839</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -4517,13 +4517,13 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4.237319201299675e-17</v>
+        <v>-6.6479308875418e-16</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.715856455137496e-17</v>
+        <v>2.654651198196905e-16</v>
       </c>
       <c r="O15" t="n">
-        <v>0.00577350269189637</v>
+        <v>0.005773502691895886</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -4535,13 +4535,13 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.005000000000000112</v>
+        <v>-0.004999999999999547</v>
       </c>
       <c r="T15" t="n">
-        <v>8.673617379884035e-18</v>
+        <v>7.546047120499111e-17</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.58091034875743e-17</v>
+        <v>-1.925891125394515e-16</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -4553,13 +4553,13 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.005000000000000111</v>
+        <v>-0.004999999999999546</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.002886751345948162</v>
+        <v>0.002886751345948173</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.237319201299675e-17</v>
+        <v>-6.6479308875418e-16</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -4571,7 +4571,7 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>-1.13686837721616e-13</v>
+        <v>-1.70530256582424e-13</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -4589,7 +4589,7 @@
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.13686837721616e-13</v>
+        <v>1.70530256582424e-13</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -4621,19 +4621,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E16" t="n">
-        <v>5.374947786592948e-13</v>
+        <v>1.65922301238304e-12</v>
       </c>
       <c r="F16" t="n">
-        <v>1.343736946648237e-10</v>
+        <v>4.148057530957601e-10</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.58091034875743e-17</v>
+        <v>-1.925891125394515e-16</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.002500000000000048</v>
+        <v>-0.002499999999999708</v>
       </c>
       <c r="I16" t="n">
-        <v>0.004330127018922295</v>
+        <v>0.004330127018921839</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -4645,13 +4645,13 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-6.63157692652396e-17</v>
+        <v>-5.600381307339044e-16</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.005000000000000043</v>
+        <v>-0.004999999999999622</v>
       </c>
       <c r="O16" t="n">
-        <v>0.008660254037844498</v>
+        <v>0.008660254037843944</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -4663,13 +4663,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>9.107298248878237e-18</v>
+        <v>7.589415207398531e-17</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.005000000000000112</v>
+        <v>-0.004999999999999546</v>
       </c>
       <c r="U16" t="n">
-        <v>1.58091034875743e-17</v>
+        <v>1.925891125394515e-16</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -4681,13 +4681,13 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.908195823574488e-17</v>
+        <v>1.066854937725736e-16</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0.01000000000000012</v>
+        <v>-0.009999999999999428</v>
       </c>
       <c r="AA16" t="n">
-        <v>6.63157692652396e-17</v>
+        <v>5.600381307339044e-16</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -4699,7 +4699,7 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>-5.374947786592948e-13</v>
+        <v>-1.65922301238304e-12</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -4717,7 +4717,7 @@
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>5.374947786592948e-13</v>
+        <v>1.65922301238304e-12</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -4749,19 +4749,19 @@
         <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.642919299551295e-13</v>
+        <v>-2.023844055306275e-13</v>
       </c>
       <c r="F17" t="n">
-        <v>-9.107298248878237e-11</v>
+        <v>-5.059610138265687e-11</v>
       </c>
       <c r="G17" t="n">
-        <v>4.237319201299675e-17</v>
+        <v>-6.6479308875418e-16</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.715856455137496e-17</v>
+        <v>2.654651198196905e-16</v>
       </c>
       <c r="I17" t="n">
-        <v>0.00577350269189637</v>
+        <v>0.005773502691895886</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -4773,13 +4773,13 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-6.63157692652396e-17</v>
+        <v>-5.600381307339044e-16</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.005000000000000043</v>
+        <v>-0.004999999999999622</v>
       </c>
       <c r="O17" t="n">
-        <v>0.008660254037844498</v>
+        <v>0.008660254037843944</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -4791,13 +4791,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.005000000000000083</v>
+        <v>0.004999999999999811</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.002886751345948208</v>
+        <v>-0.002886751345947713</v>
       </c>
       <c r="U17" t="n">
-        <v>-4.237319201299675e-17</v>
+        <v>6.6479308875418e-16</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -4809,13 +4809,13 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.005000000000000076</v>
+        <v>0.004999999999999807</v>
       </c>
       <c r="Z17" t="n">
-        <v>-0.00866025403784448</v>
+        <v>-0.008660254037843838</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.63157692652396e-17</v>
+        <v>5.600381307339044e-16</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -4827,7 +4827,7 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>3.694822225952521e-13</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -4845,7 +4845,7 @@
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>-3.694822225952521e-13</v>
+        <v>-2.273736754432321e-13</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -4877,19 +4877,19 @@
         <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>-466.6666666666679</v>
+        <v>-466.6666666666582</v>
       </c>
       <c r="F18" t="n">
-        <v>-116666.666666667</v>
+        <v>-116666.6666666645</v>
       </c>
       <c r="G18" t="n">
-        <v>4.237319201299675e-17</v>
+        <v>-6.6479308875418e-16</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.715856455137496e-17</v>
+        <v>2.654651198196905e-16</v>
       </c>
       <c r="I18" t="n">
-        <v>0.00577350269189637</v>
+        <v>0.005773502691895886</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -4901,13 +4901,13 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.02000000000000019</v>
+        <v>0.01999999999999778</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.01000000000000005</v>
+        <v>-0.009999999999999554</v>
       </c>
       <c r="O18" t="n">
-        <v>0.005773502691896366</v>
+        <v>0.005773502691895859</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -4919,13 +4919,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.715856455137496e-17</v>
+        <v>2.654651198196905e-16</v>
       </c>
       <c r="T18" t="n">
-        <v>-4.237319201299675e-17</v>
+        <v>6.6479308875418e-16</v>
       </c>
       <c r="U18" t="n">
-        <v>0.00577350269189637</v>
+        <v>0.005773502691895886</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -4937,13 +4937,13 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>-0.01000000000000005</v>
+        <v>-0.009999999999999554</v>
       </c>
       <c r="Z18" t="n">
-        <v>-0.02000000000000019</v>
+        <v>-0.01999999999999778</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.005773502691896366</v>
+        <v>0.005773502691895859</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -4955,7 +4955,7 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.364242052659392e-12</v>
+        <v>-8.29913915367797e-12</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -4973,7 +4973,7 @@
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>-1.364242052659392e-12</v>
+        <v>8.29913915367797e-12</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -5005,19 +5005,19 @@
         <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>-8.095376221225099e-14</v>
+        <v>-2.42861286636753e-13</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.023844055306275e-11</v>
+        <v>-6.071532165918825e-11</v>
       </c>
       <c r="G19" t="n">
-        <v>-6.63157692652396e-17</v>
+        <v>-5.600381307339044e-16</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.005000000000000043</v>
+        <v>-0.004999999999999622</v>
       </c>
       <c r="I19" t="n">
-        <v>0.008660254037844498</v>
+        <v>0.008660254037843944</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -5029,13 +5029,13 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.02000000000000019</v>
+        <v>0.01999999999999778</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.01000000000000005</v>
+        <v>-0.009999999999999554</v>
       </c>
       <c r="O19" t="n">
-        <v>0.005773502691896366</v>
+        <v>0.005773502691895859</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -5047,13 +5047,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.01000000000000012</v>
+        <v>-0.009999999999999428</v>
       </c>
       <c r="T19" t="n">
-        <v>1.821459649775647e-17</v>
+        <v>1.058181320345852e-16</v>
       </c>
       <c r="U19" t="n">
-        <v>-6.63157692652396e-17</v>
+        <v>-5.600381307339044e-16</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -5065,13 +5065,13 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>-0.01000000000000012</v>
+        <v>-0.009999999999999433</v>
       </c>
       <c r="Z19" t="n">
-        <v>-0.00577350269189625</v>
+        <v>-0.005773502691896071</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.02000000000000019</v>
+        <v>0.01999999999999778</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -5083,7 +5083,7 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -5101,7 +5101,7 @@
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>-5.684341886080801e-14</v>
+        <v>-2.273736754432321e-13</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -5133,19 +5133,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E20" t="n">
-        <v>6.54341469672185e-13</v>
+        <v>-7.478188224824971e-13</v>
       </c>
       <c r="F20" t="n">
-        <v>1.635853674180462e-10</v>
+        <v>-1.869547056206243e-10</v>
       </c>
       <c r="G20" t="n">
-        <v>-6.63157692652396e-17</v>
+        <v>-5.600381307339044e-16</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.005000000000000043</v>
+        <v>-0.004999999999999622</v>
       </c>
       <c r="I20" t="n">
-        <v>0.008660254037844498</v>
+        <v>0.008660254037843944</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -5157,13 +5157,13 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.03000000000000023</v>
+        <v>0.02999999999999752</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.007500000000000036</v>
+        <v>-0.007499999999999597</v>
       </c>
       <c r="O20" t="n">
-        <v>0.004330127018922292</v>
+        <v>0.004330127018921823</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -5175,13 +5175,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.008660254037844478</v>
+        <v>-0.008660254037843838</v>
       </c>
       <c r="T20" t="n">
-        <v>0.005000000000000075</v>
+        <v>0.004999999999999805</v>
       </c>
       <c r="U20" t="n">
-        <v>-6.63157692652396e-17</v>
+        <v>-5.600381307339044e-16</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -5193,13 +5193,13 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>-0.008660254037844466</v>
+        <v>-0.008660254037843852</v>
       </c>
       <c r="Z20" t="n">
-        <v>6.722053469410127e-17</v>
+        <v>-1.196959198423997e-16</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.03000000000000023</v>
+        <v>0.02999999999999752</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -5211,7 +5211,7 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>-6.821210263296962e-13</v>
+        <v>7.389644451905042e-13</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -5229,7 +5229,7 @@
         <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>6.821210263296962e-13</v>
+        <v>-7.389644451905042e-13</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -5261,19 +5261,19 @@
         <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>8.095376221225099e-14</v>
+        <v>2.833381677428785e-13</v>
       </c>
       <c r="F21" t="n">
-        <v>2.023844055306275e-11</v>
+        <v>7.083454193571961e-11</v>
       </c>
       <c r="G21" t="n">
-        <v>0.02000000000000019</v>
+        <v>0.01999999999999778</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.01000000000000005</v>
+        <v>-0.009999999999999554</v>
       </c>
       <c r="I21" t="n">
-        <v>0.005773502691896366</v>
+        <v>0.005773502691895859</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -5285,13 +5285,13 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.03000000000000023</v>
+        <v>0.02999999999999752</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.007500000000000036</v>
+        <v>-0.007499999999999597</v>
       </c>
       <c r="O21" t="n">
-        <v>0.004330127018922292</v>
+        <v>0.004330127018921823</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -5303,13 +5303,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>6.678685382510707e-17</v>
+        <v>-1.222980050563649e-16</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.01154700538379262</v>
+        <v>-0.01154700538379193</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.02000000000000019</v>
+        <v>-0.01999999999999778</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -5321,13 +5321,13 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>6.765421556309548e-17</v>
+        <v>-1.192622389734055e-16</v>
       </c>
       <c r="Z21" t="n">
-        <v>-0.008660254037844468</v>
+        <v>-0.008660254037843852</v>
       </c>
       <c r="AA21" t="n">
-        <v>-0.03000000000000023</v>
+        <v>-0.02999999999999752</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -5339,7 +5339,7 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>-8.095376221225073e-14</v>
+        <v>-2.833381677428796e-13</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>8.095376221225073e-14</v>
+        <v>2.833381677428796e-13</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -5389,19 +5389,19 @@
         <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.376213957608267e-12</v>
+        <v>4.776271970522808e-12</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.440534894020667e-10</v>
+        <v>1.194067992630702e-09</v>
       </c>
       <c r="G22" t="n">
-        <v>0.02000000000000019</v>
+        <v>0.01999999999999778</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.01000000000000005</v>
+        <v>-0.009999999999999554</v>
       </c>
       <c r="I22" t="n">
-        <v>0.005773502691896366</v>
+        <v>0.005773502691895859</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -5413,10 +5413,10 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0600000000000005</v>
+        <v>0.05999999999999572</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.01000000000000008</v>
+        <v>-0.009999999999999452</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -5431,13 +5431,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.01000000000000005</v>
+        <v>-0.009999999999999554</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.02000000000000019</v>
+        <v>-0.01999999999999778</v>
       </c>
       <c r="U22" t="n">
-        <v>0.005773502691896366</v>
+        <v>0.005773502691895859</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -5449,10 +5449,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>-0.01000000000000008</v>
+        <v>-0.009999999999999452</v>
       </c>
       <c r="Z22" t="n">
-        <v>-0.0600000000000005</v>
+        <v>-0.05999999999999572</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.364242052659392e-12</v>
+        <v>-4.774847184307873e-12</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -5485,7 +5485,7 @@
         <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>-1.364242052659392e-12</v>
+        <v>4.774847184307873e-12</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -5517,19 +5517,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E23" t="n">
-        <v>4.673867640515606e-13</v>
+        <v>-3.178229995550613e-12</v>
       </c>
       <c r="F23" t="n">
-        <v>1.168466910128902e-10</v>
+        <v>-7.945574988876531e-10</v>
       </c>
       <c r="G23" t="n">
-        <v>0.03000000000000023</v>
+        <v>0.02999999999999752</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.007500000000000036</v>
+        <v>-0.007499999999999597</v>
       </c>
       <c r="I23" t="n">
-        <v>0.004330127018922292</v>
+        <v>0.004330127018921823</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -5541,10 +5541,10 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0600000000000005</v>
+        <v>0.05999999999999572</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.01000000000000008</v>
+        <v>-0.009999999999999452</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -5559,13 +5559,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.008660254037844466</v>
+        <v>-0.008660254037843852</v>
       </c>
       <c r="T23" t="n">
-        <v>6.722053469410127e-17</v>
+        <v>-1.196959198423997e-16</v>
       </c>
       <c r="U23" t="n">
-        <v>0.03000000000000023</v>
+        <v>0.02999999999999752</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -5577,13 +5577,13 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>-0.008660254037844458</v>
+        <v>-0.008660254037843911</v>
       </c>
       <c r="Z23" t="n">
-        <v>-0.005000000000000042</v>
+        <v>-0.004999999999999726</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.0600000000000005</v>
+        <v>0.05999999999999572</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -5595,7 +5595,7 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>-4.547473508864641e-13</v>
+        <v>3.183231456205249e-12</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -5613,7 +5613,7 @@
         <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>4.547473508864641e-13</v>
+        <v>-3.183231456205249e-12</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -5645,10 +5645,10 @@
         <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.051310084408792e-14</v>
+        <v>-1.564522602645751e-12</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.012827521102198e-11</v>
+        <v>-3.911306506614377e-10</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -5669,7 +5669,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-4.340689376152277e-19</v>
+        <v>-1.676274217120448e-17</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>-4.340689376152277e-19</v>
+        <v>-1.676274217120448e-17</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -5723,7 +5723,7 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>4.051310084408793e-14</v>
+        <v>1.564522602645751e-12</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -5741,7 +5741,7 @@
         <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>-4.051310084408793e-14</v>
+        <v>-1.564522602645751e-12</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -5773,19 +5773,19 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.698281960933733e-14</v>
+        <v>6.7371775228936e-14</v>
       </c>
       <c r="F25" t="n">
-        <v>6.745704902334333e-12</v>
+        <v>1.6842943807234e-11</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.609820512624577e-17</v>
+        <v>-1.93310952988333e-16</v>
       </c>
       <c r="H25" t="n">
-        <v>0.002500000000000045</v>
+        <v>0.002499999999999709</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.004330127018922291</v>
+        <v>-0.004330127018921833</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -5797,13 +5797,13 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.58091034875743e-17</v>
+        <v>-1.925891125394515e-16</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.002500000000000048</v>
+        <v>-0.002499999999999708</v>
       </c>
       <c r="O25" t="n">
-        <v>0.004330127018922295</v>
+        <v>0.004330127018921839</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -5815,13 +5815,13 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.609820512624577e-17</v>
+        <v>-1.93310952988333e-16</v>
       </c>
       <c r="T25" t="n">
-        <v>0.002500000000000045</v>
+        <v>0.002499999999999709</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.004330127018922291</v>
+        <v>-0.004330127018921833</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -5833,13 +5833,13 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>-1.58091034875743e-17</v>
+        <v>-1.925891125394515e-16</v>
       </c>
       <c r="Z25" t="n">
-        <v>-0.002500000000000048</v>
+        <v>-0.002499999999999708</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.004330127018922295</v>
+        <v>0.004330127018921839</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -5851,7 +5851,7 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>-2.698281960933742e-14</v>
+        <v>-6.737177522893694e-14</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -5869,7 +5869,7 @@
         <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.698281960933742e-14</v>
+        <v>6.737177522893694e-14</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -5901,19 +5901,19 @@
         <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>1.805021047112535e-14</v>
+        <v>8.200201145028953e-14</v>
       </c>
       <c r="F26" t="n">
-        <v>4.512552617781336e-12</v>
+        <v>2.050050286257238e-11</v>
       </c>
       <c r="G26" t="n">
-        <v>4.217979690080612e-17</v>
+        <v>-6.656716817340045e-16</v>
       </c>
       <c r="H26" t="n">
-        <v>2.496555289566721e-17</v>
+        <v>-2.662702988502231e-16</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.005773502691896366</v>
+        <v>-0.005773502691895882</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -5925,13 +5925,13 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>4.237319201299675e-17</v>
+        <v>-6.6479308875418e-16</v>
       </c>
       <c r="N26" t="n">
-        <v>-2.715856455137496e-17</v>
+        <v>2.654651198196905e-16</v>
       </c>
       <c r="O26" t="n">
-        <v>0.00577350269189637</v>
+        <v>0.005773502691895886</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -5943,13 +5943,13 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>4.217979690080612e-17</v>
+        <v>-6.656716817340045e-16</v>
       </c>
       <c r="T26" t="n">
-        <v>2.496555289566721e-17</v>
+        <v>-2.662702988502231e-16</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.005773502691896366</v>
+        <v>-0.005773502691895882</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -5961,13 +5961,13 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>4.237319201299675e-17</v>
+        <v>-6.6479308875418e-16</v>
       </c>
       <c r="Z26" t="n">
-        <v>-2.715856455137496e-17</v>
+        <v>2.654651198196905e-16</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.00577350269189637</v>
+        <v>0.005773502691895886</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -5979,7 +5979,7 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>-1.805021047112511e-14</v>
+        <v>-8.200201145029306e-14</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
@@ -5997,7 +5997,7 @@
         <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.805021047112511e-14</v>
+        <v>8.200201145029306e-14</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -6029,19 +6029,19 @@
         <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>8.39681862670618e-15</v>
+        <v>6.565904309215647e-15</v>
       </c>
       <c r="F27" t="n">
-        <v>2.099204656676545e-12</v>
+        <v>1.641476077303912e-12</v>
       </c>
       <c r="G27" t="n">
-        <v>-6.640573517909717e-17</v>
+        <v>-5.60108479708646e-16</v>
       </c>
       <c r="H27" t="n">
-        <v>0.005000000000000042</v>
+        <v>0.004999999999999626</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.008660254037844501</v>
+        <v>-0.008660254037843948</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -6053,13 +6053,13 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-6.63157692652396e-17</v>
+        <v>-5.600381307339044e-16</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.005000000000000043</v>
+        <v>-0.004999999999999622</v>
       </c>
       <c r="O27" t="n">
-        <v>0.008660254037844498</v>
+        <v>0.008660254037843944</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -6071,13 +6071,13 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>-6.640573517909717e-17</v>
+        <v>-5.60108479708646e-16</v>
       </c>
       <c r="T27" t="n">
-        <v>0.005000000000000042</v>
+        <v>0.004999999999999626</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.008660254037844501</v>
+        <v>-0.008660254037843948</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -6089,13 +6089,13 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>-6.63157692652396e-17</v>
+        <v>-5.600381307339044e-16</v>
       </c>
       <c r="Z27" t="n">
-        <v>-0.005000000000000043</v>
+        <v>-0.004999999999999622</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.008660254037844498</v>
+        <v>0.008660254037843944</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -6107,7 +6107,7 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>-8.396818626705484e-15</v>
+        <v>-6.565904309210424e-15</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
@@ -6125,7 +6125,7 @@
         <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>8.396818626705484e-15</v>
+        <v>6.565904309210424e-15</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -6163,13 +6163,13 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.02000000000000019</v>
+        <v>0.01999999999999778</v>
       </c>
       <c r="H28" t="n">
-        <v>0.01000000000000005</v>
+        <v>0.009999999999999551</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.005773502691896375</v>
+        <v>-0.005773502691895869</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -6181,13 +6181,13 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.02000000000000019</v>
+        <v>0.01999999999999778</v>
       </c>
       <c r="N28" t="n">
-        <v>-0.01000000000000005</v>
+        <v>-0.009999999999999554</v>
       </c>
       <c r="O28" t="n">
-        <v>0.005773502691896366</v>
+        <v>0.005773502691895859</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -6199,13 +6199,13 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.02000000000000019</v>
+        <v>0.01999999999999778</v>
       </c>
       <c r="T28" t="n">
-        <v>0.01000000000000005</v>
+        <v>0.009999999999999551</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.005773502691896375</v>
+        <v>-0.005773502691895869</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -6217,13 +6217,13 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.02000000000000019</v>
+        <v>0.01999999999999778</v>
       </c>
       <c r="Z28" t="n">
-        <v>-0.01000000000000005</v>
+        <v>-0.009999999999999554</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.005773502691896366</v>
+        <v>0.005773502691895859</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -6291,13 +6291,13 @@
         <v>-8.095376221225099e-11</v>
       </c>
       <c r="G29" t="n">
-        <v>0.03000000000000024</v>
+        <v>0.02999999999999752</v>
       </c>
       <c r="H29" t="n">
-        <v>0.007500000000000032</v>
+        <v>0.007499999999999598</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.004330127018922303</v>
+        <v>-0.004330127018921832</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -6309,13 +6309,13 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.03000000000000023</v>
+        <v>0.02999999999999752</v>
       </c>
       <c r="N29" t="n">
-        <v>-0.007500000000000036</v>
+        <v>-0.007499999999999597</v>
       </c>
       <c r="O29" t="n">
-        <v>0.004330127018922292</v>
+        <v>0.004330127018921823</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
@@ -6327,13 +6327,13 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0.03000000000000024</v>
+        <v>0.02999999999999752</v>
       </c>
       <c r="T29" t="n">
-        <v>0.007500000000000032</v>
+        <v>0.007499999999999598</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.004330127018922303</v>
+        <v>-0.004330127018921832</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -6345,13 +6345,13 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.03000000000000023</v>
+        <v>0.02999999999999752</v>
       </c>
       <c r="Z29" t="n">
-        <v>-0.007500000000000036</v>
+        <v>-0.007499999999999597</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.004330127018922292</v>
+        <v>0.004330127018921823</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -6413,16 +6413,16 @@
         <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>6.476300976980079e-13</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>1.61907524424502e-10</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0600000000000005</v>
+        <v>0.05999999999999572</v>
       </c>
       <c r="H30" t="n">
-        <v>0.01000000000000008</v>
+        <v>0.009999999999999454</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -6437,10 +6437,10 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.0600000000000005</v>
+        <v>0.05999999999999572</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.01000000000000008</v>
+        <v>-0.009999999999999452</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -6455,10 +6455,10 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0.0600000000000005</v>
+        <v>0.05999999999999572</v>
       </c>
       <c r="T30" t="n">
-        <v>0.01000000000000008</v>
+        <v>0.009999999999999454</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -6473,10 +6473,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.0600000000000005</v>
+        <v>0.05999999999999572</v>
       </c>
       <c r="Z30" t="n">
-        <v>-0.01000000000000008</v>
+        <v>-0.009999999999999452</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -6541,10 +6541,10 @@
         <v>6</v>
       </c>
       <c r="E31" t="n">
-        <v>1.011922027653137e-14</v>
+        <v>-1.426810058990924e-12</v>
       </c>
       <c r="F31" t="n">
-        <v>2.529805069132844e-12</v>
+        <v>-3.56702514747731e-10</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -6565,13 +6565,13 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-1.58091034875743e-17</v>
+        <v>-1.925891125394515e-16</v>
       </c>
       <c r="N31" t="n">
-        <v>-0.002500000000000048</v>
+        <v>-0.002499999999999708</v>
       </c>
       <c r="O31" t="n">
-        <v>0.004330127018922295</v>
+        <v>0.004330127018921839</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
@@ -6601,13 +6601,13 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.168404344971009e-19</v>
+        <v>-3.057450126409123e-17</v>
       </c>
       <c r="Z31" t="n">
-        <v>-0.003779644730092345</v>
+        <v>-0.003779644730091796</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.003273268353539973</v>
+        <v>0.003273268353539744</v>
       </c>
       <c r="AB31" t="n">
         <v>0</v>
@@ -6619,7 +6619,7 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>-1.011922027653138e-14</v>
+        <v>1.426810058990924e-12</v>
       </c>
       <c r="AF31" t="n">
         <v>0</v>
@@ -6637,7 +6637,7 @@
         <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.011922027653138e-14</v>
+        <v>-1.426810058990924e-12</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -6669,13 +6669,13 @@
         <v>6</v>
       </c>
       <c r="E32" t="n">
-        <v>-5.060515631714747e-14</v>
+        <v>1.187467712477457e-12</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.265128907928687e-11</v>
+        <v>2.968669281193641e-10</v>
       </c>
       <c r="G32" t="n">
-        <v>-4.340689376152277e-19</v>
+        <v>-1.676274217120448e-17</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -6693,13 +6693,13 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-1.609820512624577e-17</v>
+        <v>-1.93310952988333e-16</v>
       </c>
       <c r="N32" t="n">
-        <v>0.002500000000000045</v>
+        <v>0.002499999999999709</v>
       </c>
       <c r="O32" t="n">
-        <v>-0.004330127018922291</v>
+        <v>-0.004330127018921833</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
@@ -6711,13 +6711,13 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>2.170344688076139e-19</v>
+        <v>8.381371085602238e-18</v>
       </c>
       <c r="T32" t="n">
-        <v>-2.46093955883122e-19</v>
+        <v>-9.503581516393274e-18</v>
       </c>
       <c r="U32" t="n">
-        <v>2.841648233501208e-19</v>
+        <v>1.097379069351042e-17</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -6729,13 +6729,13 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>-8.673617379884035e-19</v>
+        <v>3.382710778154774e-17</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.003779644730092341</v>
+        <v>0.003779644730091793</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.00327326835353997</v>
+        <v>0.00327326835353974</v>
       </c>
       <c r="AB32" t="n">
         <v>0</v>
@@ -6747,7 +6747,7 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>5.060515631714749e-14</v>
+        <v>-1.187467712477457e-12</v>
       </c>
       <c r="AF32" t="n">
         <v>0</v>
@@ -6765,7 +6765,7 @@
         <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>-5.060515631714749e-14</v>
+        <v>1.187467712477457e-12</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -6797,10 +6797,10 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E33" t="n">
-        <v>-2.229534923420594e-13</v>
+        <v>-2.498773183476249e-12</v>
       </c>
       <c r="F33" t="n">
-        <v>-5.573837308551484e-11</v>
+        <v>-6.246932958690621e-10</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -6821,13 +6821,13 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>4.237319201299675e-17</v>
+        <v>-6.6479308875418e-16</v>
       </c>
       <c r="N33" t="n">
-        <v>-2.715856455137496e-17</v>
+        <v>2.654651198196905e-16</v>
       </c>
       <c r="O33" t="n">
-        <v>0.00577350269189637</v>
+        <v>0.005773502691895886</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -6857,13 +6857,13 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>-5.341491050333823e-18</v>
+        <v>-5.986528605649763e-17</v>
       </c>
       <c r="Z33" t="n">
-        <v>-5.004541440752285e-17</v>
+        <v>7.133286256849499e-16</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.00577350269189637</v>
+        <v>0.005773502691895886</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
@@ -6875,7 +6875,7 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.229534923420593e-13</v>
+        <v>2.498773183476248e-12</v>
       </c>
       <c r="AF33" t="n">
         <v>0</v>
@@ -6893,7 +6893,7 @@
         <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>-2.229534923420593e-13</v>
+        <v>-2.498773183476248e-12</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -6925,13 +6925,13 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E34" t="n">
-        <v>1.36588479121044e-13</v>
+        <v>2.172209048097271e-12</v>
       </c>
       <c r="F34" t="n">
-        <v>3.414711978026099e-11</v>
+        <v>5.430522620243177e-10</v>
       </c>
       <c r="G34" t="n">
-        <v>-4.340689376152277e-19</v>
+        <v>-1.676274217120448e-17</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -6949,13 +6949,13 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>4.217979690080612e-17</v>
+        <v>-6.656716817340045e-16</v>
       </c>
       <c r="N34" t="n">
-        <v>2.496555289566721e-17</v>
+        <v>-2.662702988502231e-16</v>
       </c>
       <c r="O34" t="n">
-        <v>-0.005773502691896366</v>
+        <v>-0.005773502691895882</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
@@ -6967,10 +6967,10 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1.941215302857529e-19</v>
+        <v>7.496526196823125e-18</v>
       </c>
       <c r="T34" t="n">
-        <v>-3.882430605715059e-19</v>
+        <v>-1.499305239364625e-17</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -6985,13 +6985,13 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>3.46649071876395e-18</v>
+        <v>5.953803076345464e-17</v>
       </c>
       <c r="Z34" t="n">
-        <v>4.889169193305069e-17</v>
+        <v>-7.144745501451922e-16</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.005773502691896366</v>
+        <v>0.005773502691895882</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
@@ -7003,7 +7003,7 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>-1.365884791210439e-13</v>
+        <v>-2.172209048097271e-12</v>
       </c>
       <c r="AF34" t="n">
         <v>0</v>
@@ -7021,7 +7021,7 @@
         <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.365884791210439e-13</v>
+        <v>2.172209048097271e-12</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -7053,19 +7053,19 @@
         <v>6</v>
       </c>
       <c r="E35" t="n">
-        <v>2.023844055306275e-14</v>
+        <v>-1.315498635949079e-12</v>
       </c>
       <c r="F35" t="n">
-        <v>5.059610138265687e-12</v>
+        <v>-3.288746589872696e-10</v>
       </c>
       <c r="G35" t="n">
-        <v>-1.609820512624577e-17</v>
+        <v>-1.93310952988333e-16</v>
       </c>
       <c r="H35" t="n">
-        <v>0.002500000000000045</v>
+        <v>0.002499999999999709</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.004330127018922291</v>
+        <v>-0.004330127018921833</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -7077,13 +7077,13 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-6.63157692652396e-17</v>
+        <v>-5.600381307339044e-16</v>
       </c>
       <c r="N35" t="n">
-        <v>-0.005000000000000043</v>
+        <v>-0.004999999999999622</v>
       </c>
       <c r="O35" t="n">
-        <v>0.008660254037844498</v>
+        <v>0.008660254037843944</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -7095,13 +7095,13 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>-1.691355389077387e-17</v>
+        <v>-1.595945597898663e-16</v>
       </c>
       <c r="T35" t="n">
-        <v>0.003779644730092359</v>
+        <v>0.003779644730092012</v>
       </c>
       <c r="U35" t="n">
-        <v>-0.003273268353539949</v>
+        <v>-0.003273268353539487</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -7113,13 +7113,13 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>-1.647987302177967e-17</v>
+        <v>-1.877838162744894e-16</v>
       </c>
       <c r="Z35" t="n">
-        <v>-0.00755928946018459</v>
+        <v>-0.00755928946018376</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.006546536707079898</v>
+        <v>0.006546536707079803</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
@@ -7131,7 +7131,7 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>-2.023844055306278e-14</v>
+        <v>1.315498635949078e-12</v>
       </c>
       <c r="AF35" t="n">
         <v>0</v>
@@ -7149,7 +7149,7 @@
         <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.023844055306278e-14</v>
+        <v>-1.315498635949078e-12</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -7181,19 +7181,19 @@
         <v>6</v>
       </c>
       <c r="E36" t="n">
-        <v>-5.059610138265687e-14</v>
+        <v>1.285140975119484e-12</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.264902534566422e-11</v>
+        <v>3.212852437798711e-10</v>
       </c>
       <c r="G36" t="n">
-        <v>-1.58091034875743e-17</v>
+        <v>-1.925891125394515e-16</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.002500000000000048</v>
+        <v>-0.002499999999999708</v>
       </c>
       <c r="I36" t="n">
-        <v>0.004330127018922295</v>
+        <v>0.004330127018921839</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -7205,13 +7205,13 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-6.640573517909717e-17</v>
+        <v>-5.60108479708646e-16</v>
       </c>
       <c r="N36" t="n">
-        <v>0.005000000000000042</v>
+        <v>0.004999999999999626</v>
       </c>
       <c r="O36" t="n">
-        <v>-0.008660254037844501</v>
+        <v>-0.008660254037843948</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
@@ -7223,13 +7223,13 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>1.582935171828836e-17</v>
+        <v>1.619798045693344e-16</v>
       </c>
       <c r="T36" t="n">
-        <v>-0.003779644730092363</v>
+        <v>-0.003779644730092014</v>
       </c>
       <c r="U36" t="n">
-        <v>-0.003273268353539952</v>
+        <v>-0.003273268353539491</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -7241,13 +7241,13 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.474514954580286e-17</v>
+        <v>1.895185397504662e-16</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.007559289460184591</v>
+        <v>0.007559289460183765</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.006546536707079901</v>
+        <v>0.006546536707079806</v>
       </c>
       <c r="AB36" t="n">
         <v>0</v>
@@ -7259,7 +7259,7 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>5.059610138265691e-14</v>
+        <v>-1.285140975119486e-12</v>
       </c>
       <c r="AF36" t="n">
         <v>0</v>
@@ -7277,7 +7277,7 @@
         <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>-5.059610138265691e-14</v>
+        <v>1.285140975119486e-12</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -7309,19 +7309,19 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.264441019196233e-13</v>
+        <v>-2.396648962531799e-12</v>
       </c>
       <c r="F37" t="n">
-        <v>-3.161102547990584e-11</v>
+        <v>-5.991622406329497e-10</v>
       </c>
       <c r="G37" t="n">
-        <v>4.217979690080612e-17</v>
+        <v>-6.656716817340045e-16</v>
       </c>
       <c r="H37" t="n">
-        <v>2.496555289566721e-17</v>
+        <v>-2.662702988502231e-16</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.005773502691896366</v>
+        <v>-0.005773502691895882</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -7333,13 +7333,13 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.02000000000000019</v>
+        <v>0.01999999999999778</v>
       </c>
       <c r="N37" t="n">
-        <v>-0.01000000000000005</v>
+        <v>-0.009999999999999554</v>
       </c>
       <c r="O37" t="n">
-        <v>0.005773502691896366</v>
+        <v>0.005773502691895859</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
@@ -7351,13 +7351,13 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>4.119324797769893e-17</v>
+        <v>-5.358568216580811e-16</v>
       </c>
       <c r="T37" t="n">
-        <v>-2.656182258481926e-17</v>
+        <v>4.763151546978791e-16</v>
       </c>
       <c r="U37" t="n">
-        <v>-0.005773502691896366</v>
+        <v>-0.005773502691895882</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -7369,13 +7369,13 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>3.816391647148976e-17</v>
+        <v>-5.93275428784068e-16</v>
       </c>
       <c r="Z37" t="n">
-        <v>-0.02236067977499809</v>
+        <v>-0.02236067977499571</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.005773502691896366</v>
+        <v>0.005773502691895859</v>
       </c>
       <c r="AB37" t="n">
         <v>0</v>
@@ -7387,7 +7387,7 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.264441019196232e-13</v>
+        <v>2.396648962531798e-12</v>
       </c>
       <c r="AF37" t="n">
         <v>0</v>
@@ -7405,7 +7405,7 @@
         <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>-1.264441019196232e-13</v>
+        <v>-2.396648962531798e-12</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -7437,19 +7437,19 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E38" t="n">
-        <v>1.395193330238924e-13</v>
+        <v>2.298294889688984e-12</v>
       </c>
       <c r="F38" t="n">
-        <v>3.48798332559731e-11</v>
+        <v>5.745737224222461e-10</v>
       </c>
       <c r="G38" t="n">
-        <v>4.237319201299675e-17</v>
+        <v>-6.6479308875418e-16</v>
       </c>
       <c r="H38" t="n">
-        <v>-2.715856455137496e-17</v>
+        <v>2.654651198196905e-16</v>
       </c>
       <c r="I38" t="n">
-        <v>0.00577350269189637</v>
+        <v>0.005773502691895886</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -7461,13 +7461,13 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.02000000000000019</v>
+        <v>0.01999999999999778</v>
       </c>
       <c r="N38" t="n">
-        <v>0.01000000000000005</v>
+        <v>0.009999999999999551</v>
       </c>
       <c r="O38" t="n">
-        <v>-0.005773502691896375</v>
+        <v>-0.005773502691895869</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -7479,13 +7479,13 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>-4.324122615621858e-17</v>
+        <v>5.347437289140614e-16</v>
       </c>
       <c r="T38" t="n">
-        <v>2.575405580424665e-17</v>
+        <v>-4.758894042561681e-16</v>
       </c>
       <c r="U38" t="n">
-        <v>-0.00577350269189637</v>
+        <v>-0.005773502691895886</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -7497,13 +7497,13 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>-3.989863994746656e-17</v>
+        <v>5.898059818321144e-16</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.02236067977499809</v>
+        <v>0.02236067977499571</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.005773502691896375</v>
+        <v>0.005773502691895869</v>
       </c>
       <c r="AB38" t="n">
         <v>0</v>
@@ -7515,7 +7515,7 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>-1.395193330238923e-13</v>
+        <v>-2.298294889688983e-12</v>
       </c>
       <c r="AF38" t="n">
         <v>0</v>
@@ -7533,7 +7533,7 @@
         <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.395193330238923e-13</v>
+        <v>2.298294889688983e-12</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -7565,19 +7565,19 @@
         <v>6</v>
       </c>
       <c r="E39" t="n">
-        <v>-4.04768811061255e-14</v>
+        <v>-1.376213957608267e-12</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.011922027653137e-11</v>
+        <v>-3.440534894020667e-10</v>
       </c>
       <c r="G39" t="n">
-        <v>-6.640573517909717e-17</v>
+        <v>-5.60108479708646e-16</v>
       </c>
       <c r="H39" t="n">
-        <v>0.005000000000000042</v>
+        <v>0.004999999999999626</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.008660254037844501</v>
+        <v>-0.008660254037843948</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -7589,13 +7589,13 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.03000000000000023</v>
+        <v>0.02999999999999752</v>
       </c>
       <c r="N39" t="n">
-        <v>-0.007500000000000036</v>
+        <v>-0.007499999999999597</v>
       </c>
       <c r="O39" t="n">
-        <v>0.004330127018922292</v>
+        <v>0.004330127018921823</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
@@ -7607,13 +7607,13 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0.007500000000000047</v>
+        <v>0.00749999999999925</v>
       </c>
       <c r="T39" t="n">
-        <v>-0.0009449111825230588</v>
+        <v>-0.0009449111825227826</v>
       </c>
       <c r="U39" t="n">
-        <v>-0.006546536707079901</v>
+        <v>-0.006546536707079806</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -7625,13 +7625,13 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.007500000000000047</v>
+        <v>0.007499999999999221</v>
       </c>
       <c r="Z39" t="n">
-        <v>-0.01984313483298454</v>
+        <v>-0.01984313483298294</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.02291287847477943</v>
+        <v>0.0229128784747773</v>
       </c>
       <c r="AB39" t="n">
         <v>0</v>
@@ -7643,7 +7643,7 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>1.364242052659392e-12</v>
       </c>
       <c r="AF39" t="n">
         <v>0</v>
@@ -7661,7 +7661,7 @@
         <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>-5.684341886080801e-14</v>
+        <v>-1.364242052659392e-12</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -7693,19 +7693,19 @@
         <v>6</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>1.25478331428989e-12</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>3.136958285724726e-10</v>
       </c>
       <c r="G40" t="n">
-        <v>-6.63157692652396e-17</v>
+        <v>-5.600381307339044e-16</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.005000000000000043</v>
+        <v>-0.004999999999999622</v>
       </c>
       <c r="I40" t="n">
-        <v>0.008660254037844498</v>
+        <v>0.008660254037843944</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -7717,13 +7717,13 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.03000000000000024</v>
+        <v>0.02999999999999752</v>
       </c>
       <c r="N40" t="n">
-        <v>0.007500000000000032</v>
+        <v>0.007499999999999598</v>
       </c>
       <c r="O40" t="n">
-        <v>-0.004330127018922303</v>
+        <v>-0.004330127018921832</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
@@ -7735,13 +7735,13 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>-0.007500000000000047</v>
+        <v>-0.007499999999999245</v>
       </c>
       <c r="T40" t="n">
-        <v>0.0009449111825230567</v>
+        <v>0.0009449111825227839</v>
       </c>
       <c r="U40" t="n">
-        <v>-0.006546536707079898</v>
+        <v>-0.006546536707079803</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -7753,13 +7753,13 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>-0.007500000000000047</v>
+        <v>-0.007499999999999218</v>
       </c>
       <c r="Z40" t="n">
-        <v>0.01984313483298453</v>
+        <v>0.01984313483298294</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.02291287847477944</v>
+        <v>0.02291287847477731</v>
       </c>
       <c r="AB40" t="n">
         <v>0</v>
@@ -7771,7 +7771,7 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>-1.250555214937776e-12</v>
       </c>
       <c r="AF40" t="n">
         <v>0</v>
@@ -7789,7 +7789,7 @@
         <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.250555214937776e-12</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -7821,19 +7821,19 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E41" t="n">
-        <v>7.24072461363788e-13</v>
+        <v>-1.448144922727576e-12</v>
       </c>
       <c r="F41" t="n">
-        <v>1.81018115340947e-10</v>
+        <v>-3.62036230681894e-10</v>
       </c>
       <c r="G41" t="n">
-        <v>0.02000000000000019</v>
+        <v>0.01999999999999778</v>
       </c>
       <c r="H41" t="n">
-        <v>0.01000000000000005</v>
+        <v>0.009999999999999551</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.005773502691896375</v>
+        <v>-0.005773502691895869</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -7845,10 +7845,10 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.0600000000000005</v>
+        <v>0.05999999999999572</v>
       </c>
       <c r="N41" t="n">
-        <v>-0.01000000000000008</v>
+        <v>-0.009999999999999452</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -7863,13 +7863,13 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0.01788854381999845</v>
+        <v>0.01788854381999692</v>
       </c>
       <c r="T41" t="n">
-        <v>-0.01341640786499889</v>
+        <v>-0.01341640786499696</v>
       </c>
       <c r="U41" t="n">
-        <v>-0.005773502691896375</v>
+        <v>-0.005773502691895869</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -7881,10 +7881,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.01788854381999847</v>
+        <v>0.01788854381999689</v>
       </c>
       <c r="Z41" t="n">
-        <v>-0.05813776741499502</v>
+        <v>-0.05813776741499045</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -7899,7 +7899,7 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>-7.958078640513122e-13</v>
+        <v>1.477928890381008e-12</v>
       </c>
       <c r="AF41" t="n">
         <v>0</v>
@@ -7917,7 +7917,7 @@
         <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>7.958078640513122e-13</v>
+        <v>-1.477928890381008e-12</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7949,19 +7949,19 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E42" t="n">
-        <v>-5.792579690910304e-13</v>
+        <v>1.592959415000334e-12</v>
       </c>
       <c r="F42" t="n">
-        <v>-1.448144922727576e-10</v>
+        <v>3.982398537500833e-10</v>
       </c>
       <c r="G42" t="n">
-        <v>0.02000000000000019</v>
+        <v>0.01999999999999778</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.01000000000000005</v>
+        <v>-0.009999999999999554</v>
       </c>
       <c r="I42" t="n">
-        <v>0.005773502691896366</v>
+        <v>0.005773502691895859</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -7973,10 +7973,10 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.0600000000000005</v>
+        <v>0.05999999999999572</v>
       </c>
       <c r="N42" t="n">
-        <v>0.01000000000000008</v>
+        <v>0.009999999999999454</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -7991,13 +7991,13 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>-0.01788854381999845</v>
+        <v>-0.01788854381999693</v>
       </c>
       <c r="T42" t="n">
-        <v>0.01341640786499889</v>
+        <v>0.01341640786499695</v>
       </c>
       <c r="U42" t="n">
-        <v>-0.005773502691896366</v>
+        <v>-0.005773502691895859</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -8009,10 +8009,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>-0.01788854381999846</v>
+        <v>-0.01788854381999689</v>
       </c>
       <c r="Z42" t="n">
-        <v>0.05813776741499501</v>
+        <v>0.05813776741499045</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -8027,7 +8027,7 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>5.684341886080801e-13</v>
+        <v>-1.591615728102624e-12</v>
       </c>
       <c r="AF42" t="n">
         <v>0</v>
@@ -8045,7 +8045,7 @@
         <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>-5.684341886080801e-13</v>
+        <v>1.591615728102624e-12</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -8077,19 +8077,19 @@
         <v>6</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>-1.61907524424502e-12</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>-4.04768811061255e-10</v>
       </c>
       <c r="G43" t="n">
-        <v>0.03000000000000024</v>
+        <v>0.02999999999999752</v>
       </c>
       <c r="H43" t="n">
-        <v>0.007500000000000032</v>
+        <v>0.007499999999999598</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.004330127018922303</v>
+        <v>-0.004330127018921832</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -8101,10 +8101,10 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.0600000000000005</v>
+        <v>0.05999999999999572</v>
       </c>
       <c r="N43" t="n">
-        <v>-0.01000000000000008</v>
+        <v>-0.009999999999999452</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -8119,13 +8119,13 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.02250000000000019</v>
+        <v>0.02249999999999831</v>
       </c>
       <c r="T43" t="n">
-        <v>-0.01417366773784619</v>
+        <v>-0.0141736677378447</v>
       </c>
       <c r="U43" t="n">
-        <v>0.0163663417676995</v>
+        <v>0.01636634176769808</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -8137,13 +8137,13 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.02250000000000019</v>
+        <v>0.02249999999999827</v>
       </c>
       <c r="Z43" t="n">
-        <v>-0.04063118084849227</v>
+        <v>-0.04063118084848914</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.03927922024247896</v>
+        <v>0.03927922024247583</v>
       </c>
       <c r="AB43" t="n">
         <v>0</v>
@@ -8155,7 +8155,7 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.818989403545856e-12</v>
       </c>
       <c r="AF43" t="n">
         <v>0</v>
@@ -8173,7 +8173,7 @@
         <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>-1.818989403545856e-12</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -8205,19 +8205,19 @@
         <v>6</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>1.295260195396016e-12</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>3.23815048849004e-10</v>
       </c>
       <c r="G44" t="n">
-        <v>0.03000000000000023</v>
+        <v>0.02999999999999752</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.007500000000000036</v>
+        <v>-0.007499999999999597</v>
       </c>
       <c r="I44" t="n">
-        <v>0.004330127018922292</v>
+        <v>0.004330127018921823</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -8229,10 +8229,10 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.0600000000000005</v>
+        <v>0.05999999999999572</v>
       </c>
       <c r="N44" t="n">
-        <v>0.01000000000000008</v>
+        <v>0.009999999999999454</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -8247,13 +8247,13 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>-0.02250000000000019</v>
+        <v>-0.0224999999999983</v>
       </c>
       <c r="T44" t="n">
-        <v>0.01417366773784618</v>
+        <v>0.0141736677378447</v>
       </c>
       <c r="U44" t="n">
-        <v>0.01636634176769951</v>
+        <v>0.01636634176769809</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -8265,13 +8265,13 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>-0.02250000000000019</v>
+        <v>-0.02249999999999827</v>
       </c>
       <c r="Z44" t="n">
-        <v>0.04063118084849227</v>
+        <v>0.04063118084848914</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.03927922024247896</v>
+        <v>0.03927922024247583</v>
       </c>
       <c r="AB44" t="n">
         <v>0</v>
@@ -8283,7 +8283,7 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>-1.13686837721616e-12</v>
       </c>
       <c r="AF44" t="n">
         <v>0</v>
@@ -8301,7 +8301,7 @@
         <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.13686837721616e-12</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>

--- a/outputs/validation_truss_fab_error.xlsx
+++ b/outputs/validation_truss_fab_error.xlsx
@@ -3163,7 +3163,7 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -3419,7 +3419,7 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-2.842170943040401e-14</v>
+        <v>-4.04768811061255e-14</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3437,7 +3437,7 @@
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>4.04768811061255e-14</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -3547,7 +3547,7 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>8.412825991399586e-12</v>
+        <v>-466.666666666658</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>-8.412825991399586e-12</v>
+        <v>466.666666666658</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-3.410605131648481e-13</v>
+        <v>-3.23815048849004e-13</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3693,7 +3693,7 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.410605131648481e-13</v>
+        <v>3.23815048849004e-13</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -3803,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-7.389644451905042e-13</v>
+        <v>-7.478188224824971e-13</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -3821,7 +3821,7 @@
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>7.389644451905042e-13</v>
+        <v>7.478188224824971e-13</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -3931,7 +3931,7 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-4.047688110612496e-14</v>
+        <v>-4.04768811061255e-14</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -3949,7 +3949,7 @@
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>4.047688110612496e-14</v>
+        <v>4.04768811061255e-14</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -4059,7 +4059,7 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>4.547473508864641e-12</v>
+        <v>4.533410683886055e-12</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -4077,7 +4077,7 @@
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>-4.547473508864641e-12</v>
+        <v>-4.533410683886055e-12</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -4187,7 +4187,7 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-3.012701199622825e-12</v>
+        <v>-2.991275289929988e-12</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -4205,7 +4205,7 @@
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.012701199622825e-12</v>
+        <v>2.991275289929988e-12</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-1.238837225825223e-11</v>
+        <v>-1.238837225825222e-11</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -4333,7 +4333,7 @@
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.238837225825223e-11</v>
+        <v>1.238837225825222e-11</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -4571,7 +4571,7 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>-1.70530256582424e-13</v>
+        <v>-1.61907524424502e-13</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -4589,7 +4589,7 @@
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.70530256582424e-13</v>
+        <v>1.61907524424502e-13</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -4827,7 +4827,7 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.273736754432321e-13</v>
+        <v>2.023844055306275e-13</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -4845,7 +4845,7 @@
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>-2.273736754432321e-13</v>
+        <v>-2.023844055306275e-13</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -4955,7 +4955,7 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>-8.29913915367797e-12</v>
+        <v>466.6666666666582</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -4973,7 +4973,7 @@
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>8.29913915367797e-12</v>
+        <v>-466.6666666666582</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -5083,7 +5083,7 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.273736754432321e-13</v>
+        <v>2.42861286636753e-13</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -5101,7 +5101,7 @@
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>-2.273736754432321e-13</v>
+        <v>-2.42861286636753e-13</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -5211,7 +5211,7 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>7.389644451905042e-13</v>
+        <v>7.478188224824971e-13</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -5229,7 +5229,7 @@
         <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>-7.389644451905042e-13</v>
+        <v>-7.478188224824971e-13</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -5339,7 +5339,7 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>-2.833381677428796e-13</v>
+        <v>-2.833381677428785e-13</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.833381677428796e-13</v>
+        <v>2.833381677428785e-13</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>-4.774847184307873e-12</v>
+        <v>-4.776271970522808e-12</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -5485,7 +5485,7 @@
         <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>4.774847184307873e-12</v>
+        <v>4.776271970522808e-12</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -5595,7 +5595,7 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>3.183231456205249e-12</v>
+        <v>3.178229995550613e-12</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -5613,7 +5613,7 @@
         <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>-3.183231456205249e-12</v>
+        <v>-3.178229995550613e-12</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -5851,7 +5851,7 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>-6.737177522893694e-14</v>
+        <v>-6.7371775228936e-14</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -5869,7 +5869,7 @@
         <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>6.737177522893694e-14</v>
+        <v>6.7371775228936e-14</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -5979,7 +5979,7 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>-8.200201145029306e-14</v>
+        <v>-8.200201145028953e-14</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
@@ -5997,7 +5997,7 @@
         <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>8.200201145029306e-14</v>
+        <v>8.200201145028953e-14</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -6107,7 +6107,7 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>-6.565904309210424e-15</v>
+        <v>-6.565904309215647e-15</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
@@ -6125,7 +6125,7 @@
         <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>6.565904309210424e-15</v>
+        <v>6.565904309215647e-15</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -6235,7 +6235,7 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
@@ -6363,7 +6363,7 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>4.547473508864641e-13</v>
+        <v>3.23815048849004e-13</v>
       </c>
       <c r="AF29" t="n">
         <v>0</v>
@@ -6381,7 +6381,7 @@
         <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>-4.547473508864641e-13</v>
+        <v>-3.23815048849004e-13</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -6491,7 +6491,7 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF30" t="n">
         <v>0</v>
@@ -6875,7 +6875,7 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.498773183476248e-12</v>
+        <v>2.498773183476249e-12</v>
       </c>
       <c r="AF33" t="n">
         <v>0</v>
@@ -6893,7 +6893,7 @@
         <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>-2.498773183476248e-12</v>
+        <v>-2.498773183476249e-12</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -7131,7 +7131,7 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.315498635949078e-12</v>
+        <v>1.315498635949079e-12</v>
       </c>
       <c r="AF35" t="n">
         <v>0</v>
@@ -7149,7 +7149,7 @@
         <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>-1.315498635949078e-12</v>
+        <v>-1.315498635949079e-12</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -7259,7 +7259,7 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>-1.285140975119486e-12</v>
+        <v>-1.285140975119484e-12</v>
       </c>
       <c r="AF36" t="n">
         <v>0</v>
@@ -7277,7 +7277,7 @@
         <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.285140975119486e-12</v>
+        <v>1.285140975119484e-12</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -7387,7 +7387,7 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.396648962531798e-12</v>
+        <v>2.396648962531799e-12</v>
       </c>
       <c r="AF37" t="n">
         <v>0</v>
@@ -7405,7 +7405,7 @@
         <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>-2.396648962531798e-12</v>
+        <v>-2.396648962531799e-12</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -7515,7 +7515,7 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>-2.298294889688983e-12</v>
+        <v>-2.298294889688984e-12</v>
       </c>
       <c r="AF38" t="n">
         <v>0</v>
@@ -7533,7 +7533,7 @@
         <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>2.298294889688983e-12</v>
+        <v>2.298294889688984e-12</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -7643,7 +7643,7 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.364242052659392e-12</v>
+        <v>1.376213957608267e-12</v>
       </c>
       <c r="AF39" t="n">
         <v>0</v>
@@ -7661,7 +7661,7 @@
         <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>-1.364242052659392e-12</v>
+        <v>-1.376213957608267e-12</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -7771,7 +7771,7 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>-1.250555214937776e-12</v>
+        <v>-1.25478331428989e-12</v>
       </c>
       <c r="AF40" t="n">
         <v>0</v>
@@ -7789,7 +7789,7 @@
         <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.250555214937776e-12</v>
+        <v>1.25478331428989e-12</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -7899,7 +7899,7 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.477928890381008e-12</v>
+        <v>1.448144922727576e-12</v>
       </c>
       <c r="AF41" t="n">
         <v>0</v>
@@ -7917,7 +7917,7 @@
         <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>-1.477928890381008e-12</v>
+        <v>-1.448144922727576e-12</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -8027,7 +8027,7 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>-1.591615728102624e-12</v>
+        <v>-1.592959415000334e-12</v>
       </c>
       <c r="AF42" t="n">
         <v>0</v>
@@ -8045,7 +8045,7 @@
         <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.591615728102624e-12</v>
+        <v>1.592959415000334e-12</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -8155,7 +8155,7 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.818989403545856e-12</v>
+        <v>1.61907524424502e-12</v>
       </c>
       <c r="AF43" t="n">
         <v>0</v>
@@ -8173,7 +8173,7 @@
         <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>-1.818989403545856e-12</v>
+        <v>-1.61907524424502e-12</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -8283,7 +8283,7 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>-1.13686837721616e-12</v>
+        <v>-1.295260195396016e-12</v>
       </c>
       <c r="AF44" t="n">
         <v>0</v>
@@ -8301,7 +8301,7 @@
         <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.13686837721616e-12</v>
+        <v>1.295260195396016e-12</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
